--- a/IEF_Home/UploadedFiles/3_EI_VehicleArchetypes_Wolfram_2020_Test.xlsx
+++ b/IEF_Home/UploadedFiles/3_EI_VehicleArchetypes_Wolfram_2020_Test.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20415"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20416"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFA6F8E-21AB-4B3B-A491-77EF449EEB0B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62DF037-8C73-442B-9EF6-5372DD20F6AC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13698" windowHeight="5370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13425" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="5" r:id="rId1"/>
@@ -1068,24 +1068,12 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1097,9 +1085,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1112,9 +1097,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1131,15 +1113,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1152,9 +1128,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
@@ -1163,9 +1136,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1187,33 +1157,63 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1229,7 +1229,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1550,352 +1550,352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF917567-276E-40DD-8D48-0D1C387BC339}">
   <dimension ref="A1:Q72"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.15625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.15625" customWidth="1"/>
-    <col min="2" max="2" width="15.83984375" customWidth="1"/>
-    <col min="3" max="3" width="23.15625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.83984375" customWidth="1"/>
-    <col min="5" max="5" width="11.68359375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.3125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.83984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="3.3125" customWidth="1"/>
+    <col min="9" max="9" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="3.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E1" s="1"/>
       <c r="H1" s="10"/>
     </row>
-    <row r="2" spans="1:17" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="B2" s="17" t="s">
+    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="19"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="82"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="19"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="82"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="20"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="22" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="20" t="s">
         <v>107</v>
       </c>
       <c r="E3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="20">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="17">
         <v>1</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="83" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="22" t="s">
         <v>110</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="29"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="25"/>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="20">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="17">
         <v>2</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="31" t="s">
+      <c r="B5" s="84"/>
+      <c r="C5" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="27" t="s">
         <v>196</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="33"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="35"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="30"/>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="20">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="17">
         <v>3</v>
       </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="31" t="s">
+      <c r="B6" s="31"/>
+      <c r="C6" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="27" t="s">
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="G6" s="38" t="s">
+      <c r="G6" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="H6" s="39"/>
-      <c r="I6" s="40"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="35"/>
       <c r="L6" s="1"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="20">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="17">
         <v>4</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="85" t="s">
         <v>116</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="27" t="s">
         <v>114</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="42"/>
-      <c r="I7" s="43"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="37"/>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="20">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
         <v>5</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="31" t="s">
+      <c r="B8" s="85"/>
+      <c r="C8" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="27">
         <v>3</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="37" t="s">
+      <c r="F8" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="44"/>
-      <c r="I8" s="45"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="39"/>
       <c r="L8" s="1"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="20">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
         <v>6</v>
       </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="31" t="s">
+      <c r="B9" s="85"/>
+      <c r="C9" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="27" t="s">
         <v>210</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="38" t="s">
+      <c r="G9" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="44"/>
-      <c r="I9" s="45"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="39"/>
       <c r="L9" s="1"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="20">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
         <v>7</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="31" t="s">
+      <c r="B10" s="85"/>
+      <c r="C10" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="D10" s="87" t="s">
+      <c r="D10" s="73" t="s">
         <v>210</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="46" t="s">
+      <c r="F10" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="G10" s="47" t="s">
+      <c r="G10" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="48" t="s">
+      <c r="H10" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="I10" s="49">
+      <c r="I10" s="43">
         <v>48</v>
       </c>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="20">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
         <v>8</v>
       </c>
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="86" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="27" t="s">
         <v>211</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="37" t="s">
+      <c r="F11" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="52" t="s">
+      <c r="G11" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="H11" s="52" t="s">
+      <c r="H11" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="53" t="s">
+      <c r="I11" s="46" t="s">
         <v>9</v>
       </c>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="20">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
         <v>9</v>
       </c>
-      <c r="B12" s="54"/>
-      <c r="C12" s="55" t="s">
+      <c r="B12" s="87"/>
+      <c r="C12" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="27" t="s">
         <v>212</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="56" t="s">
+      <c r="F12" s="48" t="s">
         <v>125</v>
       </c>
-      <c r="G12" s="57">
+      <c r="G12" s="49">
         <v>1</v>
       </c>
-      <c r="H12" s="58" t="s">
+      <c r="H12" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="59"/>
+      <c r="I12" s="51"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="20">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
         <v>10</v>
       </c>
-      <c r="B13" s="54"/>
-      <c r="C13" s="55" t="s">
+      <c r="B13" s="87"/>
+      <c r="C13" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="27" t="s">
         <v>202</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F13" s="56" t="s">
+      <c r="F13" s="48" t="s">
         <v>127</v>
       </c>
-      <c r="G13" s="57">
+      <c r="G13" s="49">
         <v>1</v>
       </c>
-      <c r="H13" s="58" t="s">
+      <c r="H13" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="I13" s="59"/>
+      <c r="I13" s="51"/>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="20">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
         <v>11</v>
       </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="55" t="s">
+      <c r="B14" s="87"/>
+      <c r="C14" s="47" t="s">
         <v>129</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="27" t="s">
         <v>203</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="56" t="s">
+      <c r="F14" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="G14" s="57">
+      <c r="G14" s="49">
         <v>1</v>
       </c>
-      <c r="H14" s="58" t="s">
+      <c r="H14" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="I14" s="59"/>
+      <c r="I14" s="51"/>
       <c r="L14" s="1"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="20">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
         <v>12</v>
       </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="55" t="s">
+      <c r="B15" s="87"/>
+      <c r="C15" s="47" t="s">
         <v>132</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="27" t="s">
         <v>4</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F15" s="56" t="s">
+      <c r="F15" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="G15" s="57">
+      <c r="G15" s="49">
         <v>1</v>
       </c>
-      <c r="H15" s="58" t="s">
+      <c r="H15" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="59"/>
+      <c r="I15" s="51"/>
       <c r="L15" s="1"/>
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
@@ -1903,26 +1903,26 @@
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="20">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="17">
         <v>13</v>
       </c>
-      <c r="B16" s="54"/>
-      <c r="C16" s="55" t="s">
+      <c r="B16" s="87"/>
+      <c r="C16" s="47" t="s">
         <v>134</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="27" t="s">
         <v>4</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F16" s="60"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="58" t="s">
+      <c r="F16" s="52"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="I16" s="59"/>
+      <c r="I16" s="51"/>
       <c r="L16" s="1"/>
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
@@ -1930,24 +1930,24 @@
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="20">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
         <v>14</v>
       </c>
-      <c r="B17" s="54"/>
-      <c r="C17" s="55" t="s">
+      <c r="B17" s="87"/>
+      <c r="C17" s="47" t="s">
         <v>135</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="27" t="s">
         <v>204</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F17" s="61"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="35"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="30"/>
       <c r="L17" s="1"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
@@ -1955,24 +1955,24 @@
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="20">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
         <v>15</v>
       </c>
-      <c r="B18" s="54"/>
-      <c r="C18" s="55" t="s">
+      <c r="B18" s="87"/>
+      <c r="C18" s="47" t="s">
         <v>136</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="27" t="s">
         <v>205</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F18" s="61"/>
+      <c r="F18" s="53"/>
       <c r="G18" s="11"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="35"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="30"/>
       <c r="L18" s="1"/>
       <c r="M18" s="8"/>
       <c r="N18" s="8"/>
@@ -1980,24 +1980,24 @@
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="20">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="17">
         <v>16</v>
       </c>
-      <c r="B19" s="54"/>
-      <c r="C19" s="55" t="s">
+      <c r="B19" s="87"/>
+      <c r="C19" s="47" t="s">
         <v>137</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="27" t="s">
         <v>206</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F19" s="61"/>
+      <c r="F19" s="53"/>
       <c r="G19" s="11"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="35"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="30"/>
       <c r="L19" s="1"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
@@ -2005,24 +2005,24 @@
       <c r="P19" s="8"/>
       <c r="Q19" s="8"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="20">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="17">
         <v>17</v>
       </c>
-      <c r="B20" s="54"/>
-      <c r="C20" s="55" t="s">
+      <c r="B20" s="87"/>
+      <c r="C20" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="27" t="s">
         <v>207</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F20" s="33"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="35"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="30"/>
       <c r="L20" s="1"/>
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
@@ -2030,26 +2030,26 @@
       <c r="P20" s="8"/>
       <c r="Q20" s="8"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="20">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="17">
         <v>18</v>
       </c>
-      <c r="B21" s="63" t="s">
+      <c r="B21" s="88" t="s">
         <v>139</v>
       </c>
-      <c r="C21" s="55" t="s">
+      <c r="C21" s="47" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="27" t="s">
         <v>213</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F21" s="64"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="65"/>
-      <c r="I21" s="66"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="57"/>
       <c r="L21" s="1"/>
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
@@ -2057,15 +2057,15 @@
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="20">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="17">
         <v>19</v>
       </c>
-      <c r="B22" s="63"/>
-      <c r="C22" s="55" t="s">
+      <c r="B22" s="88"/>
+      <c r="C22" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="27" t="s">
         <v>214</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -2080,15 +2080,15 @@
       <c r="P22" s="8"/>
       <c r="Q22" s="8"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="20">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" s="17">
         <v>20</v>
       </c>
-      <c r="B23" s="63"/>
-      <c r="C23" s="51" t="s">
+      <c r="B23" s="88"/>
+      <c r="C23" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D23" s="27" t="s">
         <v>208</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -2100,20 +2100,20 @@
       <c r="I23" s="8"/>
       <c r="L23" s="1"/>
       <c r="M23" s="8"/>
-      <c r="N23" s="67"/>
+      <c r="N23" s="58"/>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="20">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="17">
         <v>21</v>
       </c>
-      <c r="B24" s="63"/>
-      <c r="C24" s="51" t="s">
+      <c r="B24" s="88"/>
+      <c r="C24" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="D24" s="68">
+      <c r="D24" s="59">
         <v>48</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -2130,22 +2130,22 @@
       <c r="P24" s="8"/>
       <c r="Q24" s="8"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="20">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="17">
         <v>22</v>
       </c>
-      <c r="B25" s="63"/>
-      <c r="C25" s="55" t="s">
+      <c r="B25" s="88"/>
+      <c r="C25" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="27" t="s">
         <v>209</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F25" s="8"/>
-      <c r="G25" s="67"/>
+      <c r="G25" s="58"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
       <c r="L25" s="1"/>
@@ -2155,17 +2155,17 @@
       <c r="P25" s="8"/>
       <c r="Q25" s="8"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="20">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="17">
         <v>23</v>
       </c>
-      <c r="B26" s="69" t="s">
+      <c r="B26" s="75" t="s">
         <v>144</v>
       </c>
-      <c r="C26" s="70" t="s">
+      <c r="C26" s="60" t="s">
         <v>145</v>
       </c>
-      <c r="D26" s="71" t="s">
+      <c r="D26" s="61" t="s">
         <v>127</v>
       </c>
       <c r="E26" s="1" t="s">
@@ -2182,15 +2182,15 @@
       <c r="P26" s="8"/>
       <c r="Q26" s="8"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="20">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="17">
         <v>24</v>
       </c>
-      <c r="B27" s="69"/>
-      <c r="C27" s="70" t="s">
+      <c r="B27" s="75"/>
+      <c r="C27" s="60" t="s">
         <v>146</v>
       </c>
-      <c r="D27" s="71">
+      <c r="D27" s="61">
         <v>7</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -2209,15 +2209,15 @@
       <c r="P27" s="8"/>
       <c r="Q27" s="8"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="20">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="17">
         <v>25</v>
       </c>
-      <c r="B28" s="69"/>
-      <c r="C28" s="70" t="s">
+      <c r="B28" s="75"/>
+      <c r="C28" s="60" t="s">
         <v>147</v>
       </c>
-      <c r="D28" s="71" t="s">
+      <c r="D28" s="61" t="s">
         <v>133</v>
       </c>
       <c r="E28" s="1" t="s">
@@ -2236,15 +2236,15 @@
       <c r="P28" s="8"/>
       <c r="Q28" s="8"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="20">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="17">
         <v>26</v>
       </c>
-      <c r="B29" s="69"/>
-      <c r="C29" s="70" t="s">
+      <c r="B29" s="75"/>
+      <c r="C29" s="60" t="s">
         <v>148</v>
       </c>
-      <c r="D29" s="71">
+      <c r="D29" s="61">
         <v>2</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -2263,15 +2263,15 @@
       <c r="P29" s="8"/>
       <c r="Q29" s="8"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="20">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="17">
         <v>27</v>
       </c>
-      <c r="B30" s="69"/>
-      <c r="C30" s="70" t="s">
+      <c r="B30" s="75"/>
+      <c r="C30" s="60" t="s">
         <v>149</v>
       </c>
-      <c r="D30" s="71" t="s">
+      <c r="D30" s="61" t="s">
         <v>218</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -2290,15 +2290,15 @@
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="20">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="17">
         <v>28</v>
       </c>
-      <c r="B31" s="69"/>
-      <c r="C31" s="70" t="s">
+      <c r="B31" s="75"/>
+      <c r="C31" s="60" t="s">
         <v>150</v>
       </c>
-      <c r="D31" s="71">
+      <c r="D31" s="61">
         <v>14</v>
       </c>
       <c r="E31" s="1" t="s">
@@ -2317,12 +2317,12 @@
       <c r="P31" s="8"/>
       <c r="Q31" s="8"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="20">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="17">
         <v>29</v>
       </c>
-      <c r="B32" s="69"/>
-      <c r="C32" s="70" t="s">
+      <c r="B32" s="75"/>
+      <c r="C32" s="60" t="s">
         <v>151</v>
       </c>
       <c r="D32" s="6" t="s">
@@ -2344,15 +2344,15 @@
       <c r="P32" s="8"/>
       <c r="Q32" s="8"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="20">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" s="17">
         <v>30</v>
       </c>
-      <c r="B33" s="69"/>
-      <c r="C33" s="70" t="s">
+      <c r="B33" s="75"/>
+      <c r="C33" s="60" t="s">
         <v>152</v>
       </c>
-      <c r="D33" s="71">
+      <c r="D33" s="61">
         <v>10</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -2367,19 +2367,19 @@
       <c r="L33" s="8"/>
       <c r="M33" s="8"/>
       <c r="N33" s="3"/>
-      <c r="O33" s="73"/>
+      <c r="O33" s="63"/>
       <c r="P33" s="8"/>
       <c r="Q33" s="8"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="20">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" s="17">
         <v>31</v>
       </c>
-      <c r="B34" s="69"/>
-      <c r="C34" s="70" t="s">
+      <c r="B34" s="75"/>
+      <c r="C34" s="60" t="s">
         <v>153</v>
       </c>
-      <c r="D34" s="72" t="s">
+      <c r="D34" s="62" t="s">
         <v>4</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -2394,19 +2394,19 @@
       <c r="L34" s="8"/>
       <c r="M34" s="8"/>
       <c r="N34" s="3"/>
-      <c r="O34" s="73"/>
+      <c r="O34" s="63"/>
       <c r="P34" s="8"/>
       <c r="Q34" s="8"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="20">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" s="17">
         <v>32</v>
       </c>
-      <c r="B35" s="69"/>
-      <c r="C35" s="70" t="s">
+      <c r="B35" s="75"/>
+      <c r="C35" s="60" t="s">
         <v>154</v>
       </c>
-      <c r="D35" s="72" t="s">
+      <c r="D35" s="62" t="s">
         <v>4</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="F35" s="8"/>
       <c r="G35" s="3"/>
-      <c r="H35" s="73"/>
+      <c r="H35" s="63"/>
       <c r="I35" s="8"/>
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
@@ -2425,15 +2425,15 @@
       <c r="P35" s="8"/>
       <c r="Q35" s="8"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="20">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" s="17">
         <v>33</v>
       </c>
-      <c r="B36" s="69"/>
-      <c r="C36" s="70" t="s">
+      <c r="B36" s="75"/>
+      <c r="C36" s="60" t="s">
         <v>155</v>
       </c>
-      <c r="D36" s="71" t="s">
+      <c r="D36" s="61" t="s">
         <v>4</v>
       </c>
       <c r="E36" s="1" t="s">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F36" s="8"/>
       <c r="G36" s="3"/>
-      <c r="H36" s="73"/>
+      <c r="H36" s="63"/>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
@@ -2452,15 +2452,15 @@
       <c r="P36" s="8"/>
       <c r="Q36" s="8"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="20">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A37" s="17">
         <v>34</v>
       </c>
-      <c r="B37" s="69"/>
-      <c r="C37" s="70" t="s">
+      <c r="B37" s="75"/>
+      <c r="C37" s="60" t="s">
         <v>156</v>
       </c>
-      <c r="D37" s="71" t="s">
+      <c r="D37" s="61" t="s">
         <v>4</v>
       </c>
       <c r="E37" s="1" t="s">
@@ -2476,15 +2476,15 @@
       <c r="P37" s="8"/>
       <c r="Q37" s="8"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="20">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A38" s="17">
         <v>35</v>
       </c>
-      <c r="B38" s="69"/>
-      <c r="C38" s="70" t="s">
+      <c r="B38" s="75"/>
+      <c r="C38" s="60" t="s">
         <v>157</v>
       </c>
-      <c r="D38" s="71" t="s">
+      <c r="D38" s="61" t="s">
         <v>4</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -2500,15 +2500,15 @@
       <c r="P38" s="8"/>
       <c r="Q38" s="8"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="20">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" s="17">
         <v>36</v>
       </c>
-      <c r="B39" s="69"/>
-      <c r="C39" s="70" t="s">
+      <c r="B39" s="75"/>
+      <c r="C39" s="60" t="s">
         <v>158</v>
       </c>
-      <c r="D39" s="71" t="s">
+      <c r="D39" s="61" t="s">
         <v>4</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -2524,15 +2524,15 @@
       <c r="P39" s="8"/>
       <c r="Q39" s="8"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="20">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" s="17">
         <v>37</v>
       </c>
-      <c r="B40" s="69"/>
-      <c r="C40" s="70" t="s">
+      <c r="B40" s="75"/>
+      <c r="C40" s="60" t="s">
         <v>159</v>
       </c>
-      <c r="D40" s="71" t="s">
+      <c r="D40" s="61" t="s">
         <v>4</v>
       </c>
       <c r="E40" s="1" t="s">
@@ -2548,15 +2548,15 @@
       <c r="P40" s="8"/>
       <c r="Q40" s="8"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="20">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" s="17">
         <v>38</v>
       </c>
-      <c r="B41" s="69"/>
-      <c r="C41" s="70" t="s">
+      <c r="B41" s="75"/>
+      <c r="C41" s="60" t="s">
         <v>160</v>
       </c>
-      <c r="D41" s="71" t="s">
+      <c r="D41" s="61" t="s">
         <v>4</v>
       </c>
       <c r="E41" s="1" t="s">
@@ -2572,15 +2572,15 @@
       <c r="P41" s="8"/>
       <c r="Q41" s="8"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="20">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42" s="17">
         <v>39</v>
       </c>
-      <c r="B42" s="69"/>
-      <c r="C42" s="70" t="s">
+      <c r="B42" s="75"/>
+      <c r="C42" s="60" t="s">
         <v>161</v>
       </c>
-      <c r="D42" s="71" t="s">
+      <c r="D42" s="61" t="s">
         <v>4</v>
       </c>
       <c r="E42" s="1" t="s">
@@ -2596,15 +2596,15 @@
       <c r="P42" s="8"/>
       <c r="Q42" s="8"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="20">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" s="17">
         <v>40</v>
       </c>
-      <c r="B43" s="69"/>
-      <c r="C43" s="70" t="s">
+      <c r="B43" s="75"/>
+      <c r="C43" s="60" t="s">
         <v>162</v>
       </c>
-      <c r="D43" s="71" t="s">
+      <c r="D43" s="61" t="s">
         <v>4</v>
       </c>
       <c r="E43" s="1" t="s">
@@ -2616,19 +2616,19 @@
       <c r="I43" s="8"/>
       <c r="M43" s="8"/>
       <c r="N43" s="3"/>
-      <c r="O43" s="67"/>
-      <c r="P43" s="74"/>
-      <c r="Q43" s="75"/>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="20">
+      <c r="O43" s="58"/>
+      <c r="P43" s="64"/>
+      <c r="Q43" s="65"/>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A44" s="17">
         <v>41</v>
       </c>
-      <c r="B44" s="69"/>
-      <c r="C44" s="70" t="s">
+      <c r="B44" s="75"/>
+      <c r="C44" s="60" t="s">
         <v>163</v>
       </c>
-      <c r="D44" s="71" t="s">
+      <c r="D44" s="61" t="s">
         <v>4</v>
       </c>
       <c r="E44" s="1" t="s">
@@ -2644,15 +2644,15 @@
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="20">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A45" s="17">
         <v>42</v>
       </c>
-      <c r="B45" s="69"/>
-      <c r="C45" s="70" t="s">
+      <c r="B45" s="75"/>
+      <c r="C45" s="60" t="s">
         <v>164</v>
       </c>
-      <c r="D45" s="71" t="s">
+      <c r="D45" s="61" t="s">
         <v>4</v>
       </c>
       <c r="E45" s="1" t="s">
@@ -2660,23 +2660,23 @@
       </c>
       <c r="F45" s="8"/>
       <c r="G45" s="3"/>
-      <c r="H45" s="67"/>
-      <c r="I45" s="74"/>
+      <c r="H45" s="58"/>
+      <c r="I45" s="64"/>
       <c r="M45" s="8"/>
       <c r="N45" s="7"/>
-      <c r="O45" s="57"/>
+      <c r="O45" s="49"/>
       <c r="P45" s="7"/>
-      <c r="Q45" s="73"/>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="20">
+      <c r="Q45" s="63"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" s="17">
         <v>43</v>
       </c>
-      <c r="B46" s="69"/>
-      <c r="C46" s="70" t="s">
+      <c r="B46" s="75"/>
+      <c r="C46" s="60" t="s">
         <v>165</v>
       </c>
-      <c r="D46" s="71" t="s">
+      <c r="D46" s="61" t="s">
         <v>4</v>
       </c>
       <c r="E46" s="1" t="s">
@@ -2688,19 +2688,19 @@
       <c r="I46" s="3"/>
       <c r="M46" s="8"/>
       <c r="N46" s="7"/>
-      <c r="O46" s="57"/>
+      <c r="O46" s="49"/>
       <c r="P46" s="7"/>
-      <c r="Q46" s="73"/>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="20">
+      <c r="Q46" s="63"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A47" s="17">
         <v>44</v>
       </c>
-      <c r="B47" s="69"/>
-      <c r="C47" s="70" t="s">
+      <c r="B47" s="75"/>
+      <c r="C47" s="60" t="s">
         <v>166</v>
       </c>
-      <c r="D47" s="71" t="s">
+      <c r="D47" s="61" t="s">
         <v>4</v>
       </c>
       <c r="E47" s="1" t="s">
@@ -2708,23 +2708,23 @@
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="7"/>
-      <c r="H47" s="76"/>
+      <c r="H47" s="66"/>
       <c r="I47" s="7"/>
       <c r="M47" s="8"/>
       <c r="N47" s="10"/>
-      <c r="O47" s="57"/>
+      <c r="O47" s="49"/>
       <c r="P47" s="7"/>
-      <c r="Q47" s="73"/>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="20">
+      <c r="Q47" s="63"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A48" s="17">
         <v>45</v>
       </c>
-      <c r="B48" s="69"/>
-      <c r="C48" s="70" t="s">
+      <c r="B48" s="75"/>
+      <c r="C48" s="60" t="s">
         <v>167</v>
       </c>
-      <c r="D48" s="71" t="s">
+      <c r="D48" s="61" t="s">
         <v>4</v>
       </c>
       <c r="E48" s="1" t="s">
@@ -2732,23 +2732,23 @@
       </c>
       <c r="F48" s="8"/>
       <c r="G48" s="7"/>
-      <c r="H48" s="57"/>
+      <c r="H48" s="49"/>
       <c r="I48" s="7"/>
       <c r="M48" s="8"/>
       <c r="N48" s="10"/>
-      <c r="O48" s="57"/>
+      <c r="O48" s="49"/>
       <c r="P48" s="7"/>
-      <c r="Q48" s="73"/>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="20">
+      <c r="Q48" s="63"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A49" s="17">
         <v>46</v>
       </c>
-      <c r="B49" s="69"/>
-      <c r="C49" s="70" t="s">
+      <c r="B49" s="75"/>
+      <c r="C49" s="60" t="s">
         <v>168</v>
       </c>
-      <c r="D49" s="71" t="s">
+      <c r="D49" s="61" t="s">
         <v>4</v>
       </c>
       <c r="E49" s="1" t="s">
@@ -2756,23 +2756,23 @@
       </c>
       <c r="F49" s="8"/>
       <c r="G49" s="10"/>
-      <c r="H49" s="57"/>
+      <c r="H49" s="49"/>
       <c r="I49" s="7"/>
       <c r="M49" s="8"/>
       <c r="N49" s="8"/>
       <c r="O49" s="8"/>
       <c r="P49" s="7"/>
-      <c r="Q49" s="73"/>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="20">
+      <c r="Q49" s="63"/>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A50" s="17">
         <v>47</v>
       </c>
-      <c r="B50" s="69"/>
-      <c r="C50" s="51" t="s">
+      <c r="B50" s="75"/>
+      <c r="C50" s="44" t="s">
         <v>169</v>
       </c>
-      <c r="D50" s="32" t="s">
+      <c r="D50" s="27" t="s">
         <v>221</v>
       </c>
       <c r="E50" s="1" t="s">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F50" s="8"/>
       <c r="G50" s="7"/>
-      <c r="H50" s="77"/>
+      <c r="H50" s="67"/>
       <c r="I50" s="7"/>
       <c r="M50" s="8"/>
       <c r="N50" s="8"/>
@@ -2788,15 +2788,15 @@
       <c r="P50" s="8"/>
       <c r="Q50" s="8"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="20">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A51" s="17">
         <v>48</v>
       </c>
-      <c r="B51" s="69"/>
-      <c r="C51" s="51" t="s">
+      <c r="B51" s="75"/>
+      <c r="C51" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="D51" s="32" t="s">
+      <c r="D51" s="27" t="s">
         <v>222</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
-      <c r="H51" s="77"/>
+      <c r="H51" s="67"/>
       <c r="I51" s="7"/>
       <c r="M51" s="8"/>
       <c r="N51" s="8"/>
@@ -2812,15 +2812,15 @@
       <c r="P51" s="8"/>
       <c r="Q51" s="8"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="20">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A52" s="17">
         <v>49</v>
       </c>
-      <c r="B52" s="69"/>
-      <c r="C52" s="51" t="s">
+      <c r="B52" s="75"/>
+      <c r="C52" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="D52" s="32" t="s">
+      <c r="D52" s="27" t="s">
         <v>223</v>
       </c>
       <c r="E52" s="1" t="s">
@@ -2828,20 +2828,20 @@
       </c>
       <c r="F52" s="8"/>
       <c r="G52" s="8"/>
-      <c r="H52" s="77"/>
+      <c r="H52" s="67"/>
       <c r="I52" s="8"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="20">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A53" s="17">
         <v>50</v>
       </c>
-      <c r="B53" s="78" t="s">
+      <c r="B53" s="76" t="s">
         <v>172</v>
       </c>
-      <c r="C53" s="31" t="s">
+      <c r="C53" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="D53" s="68" t="s">
+      <c r="D53" s="59" t="s">
         <v>198</v>
       </c>
       <c r="E53" s="1" t="s">
@@ -2852,15 +2852,15 @@
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="20">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A54" s="17">
         <v>51</v>
       </c>
-      <c r="B54" s="78"/>
-      <c r="C54" s="31" t="s">
+      <c r="B54" s="76"/>
+      <c r="C54" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="D54" s="32" t="s">
+      <c r="D54" s="27" t="s">
         <v>199</v>
       </c>
       <c r="E54" s="1" t="s">
@@ -2870,15 +2870,15 @@
       <c r="H54" s="8"/>
       <c r="I54" s="8"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="20">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A55" s="17">
         <v>52</v>
       </c>
-      <c r="B55" s="78"/>
-      <c r="C55" s="79" t="s">
+      <c r="B55" s="76"/>
+      <c r="C55" s="68" t="s">
         <v>175</v>
       </c>
-      <c r="D55" s="32" t="s">
+      <c r="D55" s="27" t="s">
         <v>200</v>
       </c>
       <c r="E55" s="1" t="s">
@@ -2888,261 +2888,261 @@
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="20">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A56" s="17">
         <v>53</v>
       </c>
-      <c r="B56" s="78"/>
-      <c r="C56" s="79" t="s">
+      <c r="B56" s="76"/>
+      <c r="C56" s="68" t="s">
         <v>176</v>
       </c>
-      <c r="D56" s="32" t="s">
+      <c r="D56" s="27" t="s">
         <v>4</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="20">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A57" s="17">
         <v>54</v>
       </c>
-      <c r="B57" s="78"/>
-      <c r="C57" s="55" t="s">
+      <c r="B57" s="76"/>
+      <c r="C57" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="D57" s="32" t="s">
+      <c r="D57" s="27" t="s">
         <v>178</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="20">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A58" s="17">
         <v>55</v>
       </c>
-      <c r="B58" s="78"/>
-      <c r="C58" s="79" t="s">
+      <c r="B58" s="76"/>
+      <c r="C58" s="68" t="s">
         <v>179</v>
       </c>
-      <c r="D58" s="32" t="s">
+      <c r="D58" s="27" t="s">
         <v>201</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="20">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A59" s="17">
         <v>56</v>
       </c>
-      <c r="B59" s="78"/>
-      <c r="C59" s="79" t="s">
+      <c r="B59" s="76"/>
+      <c r="C59" s="68" t="s">
         <v>180</v>
       </c>
-      <c r="D59" s="32" t="s">
+      <c r="D59" s="27" t="s">
         <v>201</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="20">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A60" s="17">
         <v>57</v>
       </c>
-      <c r="B60" s="78"/>
-      <c r="C60" s="31" t="s">
+      <c r="B60" s="76"/>
+      <c r="C60" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="D60" s="80">
+      <c r="D60" s="69">
         <v>1</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="20">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A61" s="17">
         <v>58</v>
       </c>
-      <c r="B61" s="81" t="s">
+      <c r="B61" s="77" t="s">
         <v>182</v>
       </c>
-      <c r="C61" s="79" t="s">
+      <c r="C61" s="68" t="s">
         <v>183</v>
       </c>
-      <c r="D61" s="82">
+      <c r="D61" s="70">
         <v>43684</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="20">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A62" s="17">
         <v>59</v>
       </c>
-      <c r="B62" s="81"/>
-      <c r="C62" s="79" t="s">
+      <c r="B62" s="77"/>
+      <c r="C62" s="68" t="s">
         <v>184</v>
       </c>
-      <c r="D62" s="82">
+      <c r="D62" s="70">
         <v>45602</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="20">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A63" s="17">
         <v>60</v>
       </c>
-      <c r="B63" s="81"/>
-      <c r="C63" s="79" t="s">
+      <c r="B63" s="77"/>
+      <c r="C63" s="68" t="s">
         <v>185</v>
       </c>
-      <c r="D63" s="32" t="s">
+      <c r="D63" s="27" t="s">
         <v>16</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="20">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A64" s="17">
         <v>61</v>
       </c>
-      <c r="B64" s="81"/>
-      <c r="C64" s="79" t="s">
+      <c r="B64" s="77"/>
+      <c r="C64" s="68" t="s">
         <v>186</v>
       </c>
-      <c r="D64" s="32" t="s">
+      <c r="D64" s="27" t="s">
         <v>197</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="20">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="17">
         <v>62</v>
       </c>
-      <c r="B65" s="81"/>
-      <c r="C65" s="31" t="s">
+      <c r="B65" s="77"/>
+      <c r="C65" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="D65" s="35"/>
+      <c r="D65" s="30"/>
       <c r="E65" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="20">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="17">
         <v>63</v>
       </c>
-      <c r="B66" s="81"/>
-      <c r="C66" s="31" t="s">
+      <c r="B66" s="77"/>
+      <c r="C66" s="26" t="s">
         <v>188</v>
       </c>
-      <c r="D66" s="35"/>
+      <c r="D66" s="30"/>
       <c r="E66" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="20">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="17">
         <v>64</v>
       </c>
-      <c r="B67" s="81"/>
-      <c r="C67" s="79" t="s">
+      <c r="B67" s="77"/>
+      <c r="C67" s="68" t="s">
         <v>189</v>
       </c>
-      <c r="D67" s="35"/>
+      <c r="D67" s="30"/>
       <c r="E67" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="20">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="17">
         <v>65</v>
       </c>
-      <c r="B68" s="83" t="s">
+      <c r="B68" s="78" t="s">
         <v>190</v>
       </c>
-      <c r="C68" s="84" t="s">
+      <c r="C68" s="71" t="s">
         <v>191</v>
       </c>
-      <c r="D68" s="35"/>
+      <c r="D68" s="30"/>
       <c r="E68" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="20">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="17">
         <v>66</v>
       </c>
-      <c r="B69" s="83"/>
-      <c r="C69" s="84" t="s">
+      <c r="B69" s="78"/>
+      <c r="C69" s="71" t="s">
         <v>192</v>
       </c>
-      <c r="D69" s="35"/>
+      <c r="D69" s="30"/>
       <c r="E69" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="20">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="17">
         <v>67</v>
       </c>
-      <c r="B70" s="83"/>
-      <c r="C70" s="84" t="s">
+      <c r="B70" s="78"/>
+      <c r="C70" s="71" t="s">
         <v>193</v>
       </c>
-      <c r="D70" s="35"/>
+      <c r="D70" s="30"/>
       <c r="E70" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="20">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="17">
         <v>68</v>
       </c>
-      <c r="B71" s="83"/>
-      <c r="C71" s="84" t="s">
+      <c r="B71" s="78"/>
+      <c r="C71" s="71" t="s">
         <v>194</v>
       </c>
-      <c r="D71" s="35"/>
+      <c r="D71" s="30"/>
       <c r="E71" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="20">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="17">
         <v>69</v>
       </c>
-      <c r="B72" s="85"/>
-      <c r="C72" s="86" t="s">
+      <c r="B72" s="79"/>
+      <c r="C72" s="72" t="s">
         <v>195</v>
       </c>
-      <c r="D72" s="66"/>
+      <c r="D72" s="57"/>
       <c r="E72" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B20"/>
+    <mergeCell ref="B21:B25"/>
     <mergeCell ref="B26:B52"/>
     <mergeCell ref="B53:B60"/>
     <mergeCell ref="B61:B67"/>
     <mergeCell ref="B68:B72"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B20"/>
-    <mergeCell ref="B21:B25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3151,35 +3151,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q481"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.1015625" customWidth="1"/>
-    <col min="2" max="2" width="10.3125" customWidth="1"/>
-    <col min="3" max="3" width="13.05078125" customWidth="1"/>
-    <col min="4" max="4" width="22.05078125" customWidth="1"/>
-    <col min="5" max="5" width="11.68359375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.26171875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.26171875" customWidth="1"/>
+    <col min="1" max="1" width="33.140625" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" customWidth="1"/>
     <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.41796875" customWidth="1"/>
-    <col min="10" max="10" width="35.578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.68359375" customWidth="1"/>
-    <col min="12" max="12" width="11.7890625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" customWidth="1"/>
+    <col min="10" max="10" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="16.9453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.41796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.68359375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.05078125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="88" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="88" t="s">
+      <c r="B1" s="74" t="s">
         <v>133</v>
       </c>
-      <c r="C1" s="88" t="s">
+      <c r="C1" s="74" t="s">
         <v>215</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -3201,7 +3201,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -3238,7 +3238,7 @@
         <v>217</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>219</v>
@@ -3259,7 +3259,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -3290,7 +3290,7 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>55</v>
       </c>
@@ -3321,7 +3321,7 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>56</v>
       </c>
@@ -3353,7 +3353,7 @@
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -3386,7 +3386,7 @@
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -3419,7 +3419,7 @@
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>59</v>
       </c>
@@ -3452,7 +3452,7 @@
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -3485,7 +3485,7 @@
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -3518,7 +3518,7 @@
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>62</v>
       </c>
@@ -3551,7 +3551,7 @@
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>63</v>
       </c>
@@ -3584,7 +3584,7 @@
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>64</v>
       </c>
@@ -3617,7 +3617,7 @@
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>65</v>
       </c>
@@ -3650,7 +3650,7 @@
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -3683,7 +3683,7 @@
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -3716,7 +3716,7 @@
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>68</v>
       </c>
@@ -3749,7 +3749,7 @@
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>69</v>
       </c>
@@ -3782,7 +3782,7 @@
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>70</v>
       </c>
@@ -3814,7 +3814,7 @@
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>71</v>
       </c>
@@ -3846,7 +3846,7 @@
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>72</v>
       </c>
@@ -3878,7 +3878,7 @@
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>73</v>
       </c>
@@ -3910,7 +3910,7 @@
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>74</v>
       </c>
@@ -3942,7 +3942,7 @@
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>75</v>
       </c>
@@ -3974,7 +3974,7 @@
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>76</v>
       </c>
@@ -4006,7 +4006,7 @@
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>77</v>
       </c>
@@ -4038,7 +4038,7 @@
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>78</v>
       </c>
@@ -4070,7 +4070,7 @@
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>79</v>
       </c>
@@ -4102,7 +4102,7 @@
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>80</v>
       </c>
@@ -4134,7 +4134,7 @@
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>81</v>
       </c>
@@ -4166,7 +4166,7 @@
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>82</v>
       </c>
@@ -4198,7 +4198,7 @@
       <c r="L32" s="6"/>
       <c r="M32" s="6"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>83</v>
       </c>
@@ -4230,7 +4230,7 @@
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>84</v>
       </c>
@@ -4263,7 +4263,7 @@
       <c r="M34" s="6"/>
       <c r="Q34" s="6"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>85</v>
       </c>
@@ -4296,7 +4296,7 @@
       <c r="M35" s="6"/>
       <c r="Q35" s="6"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>86</v>
       </c>
@@ -4329,7 +4329,7 @@
       <c r="M36" s="6"/>
       <c r="Q36" s="6"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>87</v>
       </c>
@@ -4362,7 +4362,7 @@
       <c r="M37" s="6"/>
       <c r="Q37" s="6"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>88</v>
       </c>
@@ -4395,7 +4395,7 @@
       <c r="M38" s="6"/>
       <c r="Q38" s="6"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>89</v>
       </c>
@@ -4428,7 +4428,7 @@
       <c r="M39" s="6"/>
       <c r="Q39" s="6"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -4462,7 +4462,7 @@
       <c r="N40" s="6"/>
       <c r="Q40" s="6"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -4496,7 +4496,7 @@
       <c r="N41" s="6"/>
       <c r="Q41" s="6"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>92</v>
       </c>
@@ -4530,7 +4530,7 @@
       <c r="N42" s="6"/>
       <c r="Q42" s="6"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>93</v>
       </c>
@@ -4564,7 +4564,7 @@
       <c r="N43" s="6"/>
       <c r="Q43" s="6"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>94</v>
       </c>
@@ -4598,7 +4598,7 @@
       <c r="N44" s="6"/>
       <c r="Q44" s="6"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>95</v>
       </c>
@@ -4632,7 +4632,7 @@
       <c r="N45" s="6"/>
       <c r="Q45" s="6"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>96</v>
       </c>
@@ -4664,7 +4664,7 @@
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>97</v>
       </c>
@@ -4696,7 +4696,7 @@
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>98</v>
       </c>
@@ -4728,7 +4728,7 @@
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>99</v>
       </c>
@@ -4760,7 +4760,7 @@
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
@@ -4770,7 +4770,7 @@
       <c r="N50" s="6"/>
       <c r="Q50" s="6"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
@@ -4778,7 +4778,7 @@
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
@@ -4787,7 +4787,7 @@
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="12"/>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
@@ -4799,7 +4799,7 @@
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="12"/>
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
@@ -4812,7 +4812,7 @@
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="12"/>
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
@@ -4824,7 +4824,7 @@
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="12"/>
       <c r="B56" s="12"/>
       <c r="C56" s="12"/>
@@ -4837,7 +4837,7 @@
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="12"/>
       <c r="B57" s="12"/>
       <c r="C57" s="12"/>
@@ -4849,7 +4849,7 @@
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="12"/>
       <c r="B58" s="12"/>
       <c r="C58" s="12"/>
@@ -4862,7 +4862,7 @@
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="12"/>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
@@ -4874,7 +4874,7 @@
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="12"/>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
@@ -4887,7 +4887,7 @@
       <c r="M60" s="6"/>
       <c r="N60" s="6"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="12"/>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
@@ -4899,7 +4899,7 @@
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="12"/>
       <c r="B62" s="12"/>
       <c r="C62" s="12"/>
@@ -4912,7 +4912,7 @@
       <c r="M62" s="6"/>
       <c r="N62" s="6"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="12"/>
       <c r="B63" s="12"/>
       <c r="C63" s="12"/>
@@ -4924,7 +4924,7 @@
       <c r="M63" s="6"/>
       <c r="N63" s="6"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="12"/>
       <c r="B64" s="12"/>
       <c r="C64" s="12"/>
@@ -4937,7 +4937,7 @@
       <c r="M64" s="6"/>
       <c r="N64" s="6"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="12"/>
       <c r="B65" s="12"/>
       <c r="C65" s="12"/>
@@ -4949,7 +4949,7 @@
       <c r="M65" s="6"/>
       <c r="N65" s="6"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="12"/>
       <c r="B66" s="12"/>
       <c r="C66" s="12"/>
@@ -4962,7 +4962,7 @@
       <c r="M66" s="6"/>
       <c r="N66" s="6"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="12"/>
       <c r="B67" s="12"/>
       <c r="C67" s="12"/>
@@ -4974,7 +4974,7 @@
       <c r="M67" s="6"/>
       <c r="N67" s="6"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="12"/>
       <c r="B68" s="12"/>
       <c r="C68" s="12"/>
@@ -4987,7 +4987,7 @@
       <c r="M68" s="6"/>
       <c r="N68" s="6"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="12"/>
       <c r="B69" s="12"/>
       <c r="C69" s="12"/>
@@ -4999,7 +4999,7 @@
       <c r="M69" s="6"/>
       <c r="N69" s="6"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="12"/>
       <c r="B70" s="12"/>
       <c r="C70" s="12"/>
@@ -5012,7 +5012,7 @@
       <c r="M70" s="6"/>
       <c r="N70" s="6"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="12"/>
       <c r="B71" s="12"/>
       <c r="C71" s="12"/>
@@ -5024,7 +5024,7 @@
       <c r="M71" s="6"/>
       <c r="N71" s="6"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="12"/>
       <c r="B72" s="12"/>
       <c r="C72" s="12"/>
@@ -5037,7 +5037,7 @@
       <c r="M72" s="6"/>
       <c r="N72" s="6"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="12"/>
       <c r="B73" s="12"/>
       <c r="C73" s="12"/>
@@ -5049,7 +5049,7 @@
       <c r="M73" s="6"/>
       <c r="N73" s="6"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="12"/>
       <c r="B74" s="12"/>
       <c r="C74" s="12"/>
@@ -5062,7 +5062,7 @@
       <c r="M74" s="6"/>
       <c r="N74" s="6"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="12"/>
       <c r="B75" s="12"/>
       <c r="C75" s="12"/>
@@ -5074,7 +5074,7 @@
       <c r="M75" s="6"/>
       <c r="N75" s="6"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="12"/>
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
@@ -5087,7 +5087,7 @@
       <c r="M76" s="6"/>
       <c r="N76" s="6"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="12"/>
       <c r="B77" s="12"/>
       <c r="C77" s="12"/>
@@ -5099,7 +5099,7 @@
       <c r="M77" s="6"/>
       <c r="N77" s="6"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="12"/>
       <c r="B78" s="12"/>
       <c r="C78" s="12"/>
@@ -5112,7 +5112,7 @@
       <c r="L78" s="6"/>
       <c r="M78" s="6"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="12"/>
       <c r="B79" s="12"/>
       <c r="C79" s="12"/>
@@ -5124,7 +5124,7 @@
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="12"/>
       <c r="B80" s="12"/>
       <c r="C80" s="12"/>
@@ -5137,7 +5137,7 @@
       <c r="L80" s="6"/>
       <c r="M80" s="6"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="12"/>
       <c r="B81" s="12"/>
       <c r="C81" s="12"/>
@@ -5149,7 +5149,7 @@
       <c r="L81" s="6"/>
       <c r="M81" s="6"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="12"/>
       <c r="B82" s="12"/>
       <c r="C82" s="12"/>
@@ -5162,7 +5162,7 @@
       <c r="L82" s="6"/>
       <c r="M82" s="6"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="12"/>
       <c r="B83" s="12"/>
       <c r="C83" s="12"/>
@@ -5174,7 +5174,7 @@
       <c r="L83" s="6"/>
       <c r="M83" s="6"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="12"/>
       <c r="B84" s="12"/>
       <c r="C84" s="12"/>
@@ -5187,7 +5187,7 @@
       <c r="L84" s="6"/>
       <c r="M84" s="6"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="12"/>
       <c r="B85" s="12"/>
       <c r="C85" s="12"/>
@@ -5199,7 +5199,7 @@
       <c r="L85" s="6"/>
       <c r="M85" s="6"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="12"/>
       <c r="B86" s="12"/>
       <c r="C86" s="12"/>
@@ -5212,7 +5212,7 @@
       <c r="L86" s="6"/>
       <c r="M86" s="6"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="12"/>
       <c r="B87" s="12"/>
       <c r="C87" s="12"/>
@@ -5224,7 +5224,7 @@
       <c r="L87" s="6"/>
       <c r="M87" s="6"/>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="12"/>
       <c r="B88" s="12"/>
       <c r="C88" s="12"/>
@@ -5237,7 +5237,7 @@
       <c r="L88" s="6"/>
       <c r="M88" s="6"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="12"/>
       <c r="B89" s="12"/>
       <c r="C89" s="12"/>
@@ -5249,7 +5249,7 @@
       <c r="L89" s="6"/>
       <c r="M89" s="6"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="12"/>
       <c r="B90" s="12"/>
       <c r="C90" s="12"/>
@@ -5262,7 +5262,7 @@
       <c r="L90" s="6"/>
       <c r="M90" s="6"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="12"/>
       <c r="B91" s="12"/>
       <c r="C91" s="12"/>
@@ -5274,7 +5274,7 @@
       <c r="L91" s="6"/>
       <c r="M91" s="6"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="12"/>
       <c r="B92" s="12"/>
       <c r="C92" s="12"/>
@@ -5287,7 +5287,7 @@
       <c r="L92" s="6"/>
       <c r="M92" s="6"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="12"/>
       <c r="B93" s="12"/>
       <c r="C93" s="12"/>
@@ -5299,7 +5299,7 @@
       <c r="L93" s="6"/>
       <c r="M93" s="6"/>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="12"/>
       <c r="B94" s="12"/>
       <c r="C94" s="12"/>
@@ -5312,7 +5312,7 @@
       <c r="L94" s="6"/>
       <c r="M94" s="6"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="12"/>
       <c r="B95" s="12"/>
       <c r="C95" s="12"/>
@@ -5324,7 +5324,7 @@
       <c r="L95" s="6"/>
       <c r="M95" s="6"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="12"/>
       <c r="B96" s="12"/>
       <c r="C96" s="12"/>
@@ -5337,7 +5337,7 @@
       <c r="L96" s="6"/>
       <c r="M96" s="6"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="12"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
@@ -5349,7 +5349,7 @@
       <c r="L97" s="6"/>
       <c r="M97" s="6"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="12"/>
       <c r="B98" s="12"/>
       <c r="C98" s="12"/>
@@ -5362,7 +5362,7 @@
       <c r="L98" s="6"/>
       <c r="M98" s="6"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="12"/>
       <c r="B99" s="12"/>
       <c r="C99" s="12"/>
@@ -5374,7 +5374,7 @@
       <c r="L99" s="6"/>
       <c r="M99" s="6"/>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="12"/>
       <c r="B100" s="12"/>
       <c r="C100" s="12"/>
@@ -5387,7 +5387,7 @@
       <c r="L100" s="6"/>
       <c r="M100" s="6"/>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="12"/>
       <c r="B101" s="12"/>
       <c r="C101" s="12"/>
@@ -5399,7 +5399,7 @@
       <c r="L101" s="6"/>
       <c r="M101" s="6"/>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="12"/>
       <c r="B102" s="12"/>
       <c r="C102" s="12"/>
@@ -5412,7 +5412,7 @@
       <c r="L102" s="6"/>
       <c r="M102" s="6"/>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="12"/>
       <c r="B103" s="12"/>
       <c r="C103" s="12"/>
@@ -5424,7 +5424,7 @@
       <c r="L103" s="6"/>
       <c r="M103" s="6"/>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="12"/>
       <c r="B104" s="12"/>
       <c r="C104" s="12"/>
@@ -5437,7 +5437,7 @@
       <c r="L104" s="6"/>
       <c r="M104" s="6"/>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="12"/>
       <c r="B105" s="12"/>
       <c r="C105" s="12"/>
@@ -5449,7 +5449,7 @@
       <c r="L105" s="6"/>
       <c r="M105" s="6"/>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="12"/>
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
@@ -5462,7 +5462,7 @@
       <c r="L106" s="6"/>
       <c r="M106" s="6"/>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="12"/>
       <c r="B107" s="12"/>
       <c r="C107" s="12"/>
@@ -5474,7 +5474,7 @@
       <c r="L107" s="6"/>
       <c r="M107" s="6"/>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="12"/>
       <c r="B108" s="12"/>
       <c r="C108" s="12"/>
@@ -5487,7 +5487,7 @@
       <c r="L108" s="6"/>
       <c r="M108" s="6"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="12"/>
       <c r="B109" s="12"/>
       <c r="C109" s="12"/>
@@ -5499,7 +5499,7 @@
       <c r="L109" s="6"/>
       <c r="M109" s="6"/>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="12"/>
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
@@ -5512,7 +5512,7 @@
       <c r="L110" s="6"/>
       <c r="M110" s="6"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="12"/>
       <c r="B111" s="12"/>
       <c r="C111" s="12"/>
@@ -5524,7 +5524,7 @@
       <c r="L111" s="6"/>
       <c r="M111" s="6"/>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="12"/>
       <c r="B112" s="12"/>
       <c r="C112" s="12"/>
@@ -5537,7 +5537,7 @@
       <c r="L112" s="6"/>
       <c r="M112" s="6"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="12"/>
       <c r="B113" s="12"/>
       <c r="C113" s="12"/>
@@ -5549,7 +5549,7 @@
       <c r="L113" s="6"/>
       <c r="M113" s="6"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="12"/>
       <c r="B114" s="12"/>
       <c r="C114" s="12"/>
@@ -5562,7 +5562,7 @@
       <c r="L114" s="6"/>
       <c r="M114" s="6"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="12"/>
       <c r="B115" s="12"/>
       <c r="C115" s="12"/>
@@ -5574,7 +5574,7 @@
       <c r="L115" s="6"/>
       <c r="M115" s="6"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="12"/>
       <c r="B116" s="12"/>
       <c r="C116" s="12"/>
@@ -5587,7 +5587,7 @@
       <c r="L116" s="6"/>
       <c r="M116" s="6"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="12"/>
       <c r="B117" s="12"/>
       <c r="C117" s="12"/>
@@ -5599,7 +5599,7 @@
       <c r="L117" s="6"/>
       <c r="M117" s="6"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="12"/>
       <c r="B118" s="12"/>
       <c r="C118" s="12"/>
@@ -5612,7 +5612,7 @@
       <c r="L118" s="6"/>
       <c r="M118" s="6"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="12"/>
       <c r="B119" s="12"/>
       <c r="C119" s="12"/>
@@ -5624,7 +5624,7 @@
       <c r="L119" s="6"/>
       <c r="M119" s="6"/>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="12"/>
       <c r="B120" s="12"/>
       <c r="C120" s="12"/>
@@ -5637,7 +5637,7 @@
       <c r="L120" s="6"/>
       <c r="M120" s="6"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="12"/>
       <c r="B121" s="12"/>
       <c r="C121" s="12"/>
@@ -5649,1281 +5649,1281 @@
       <c r="L121" s="6"/>
       <c r="M121" s="6"/>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D122" s="6"/>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D123" s="6"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D124" s="6"/>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D125" s="6"/>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D126" s="6"/>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D127" s="6"/>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D128" s="6"/>
     </row>
-    <row r="129" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D129" s="6"/>
       <c r="H129" s="6"/>
     </row>
-    <row r="130" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D130" s="6"/>
     </row>
-    <row r="131" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D131" s="6"/>
     </row>
-    <row r="132" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D132" s="6"/>
     </row>
-    <row r="133" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D133" s="6"/>
     </row>
-    <row r="134" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D134" s="6"/>
     </row>
-    <row r="135" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D135" s="6"/>
     </row>
-    <row r="136" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D136" s="6"/>
     </row>
-    <row r="137" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D137" s="6"/>
     </row>
-    <row r="138" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D138" s="6"/>
     </row>
-    <row r="139" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D139" s="6"/>
     </row>
-    <row r="140" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D140" s="6"/>
     </row>
-    <row r="141" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D141" s="6"/>
     </row>
-    <row r="142" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D142" s="6"/>
     </row>
-    <row r="143" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D143" s="6"/>
     </row>
-    <row r="144" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D144" s="6"/>
     </row>
-    <row r="145" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D145" s="6"/>
     </row>
-    <row r="146" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D146" s="6"/>
     </row>
-    <row r="147" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D147" s="6"/>
     </row>
-    <row r="148" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D148" s="6"/>
     </row>
-    <row r="149" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D149" s="6"/>
     </row>
-    <row r="150" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D150" s="6"/>
     </row>
-    <row r="151" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D151" s="6"/>
     </row>
-    <row r="152" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D152" s="6"/>
     </row>
-    <row r="153" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D153" s="6"/>
     </row>
-    <row r="154" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D154" s="6"/>
     </row>
-    <row r="155" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D155" s="6"/>
     </row>
-    <row r="156" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D156" s="6"/>
     </row>
-    <row r="157" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D157" s="6"/>
     </row>
-    <row r="158" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D158" s="6"/>
     </row>
-    <row r="159" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D159" s="6"/>
     </row>
-    <row r="160" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D160" s="6"/>
     </row>
-    <row r="161" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D161" s="6"/>
       <c r="H161" s="6"/>
     </row>
-    <row r="162" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D162" s="6"/>
     </row>
-    <row r="163" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D163" s="6"/>
     </row>
-    <row r="164" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D164" s="6"/>
     </row>
-    <row r="165" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D165" s="6"/>
     </row>
-    <row r="166" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D166" s="6"/>
     </row>
-    <row r="167" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D167" s="6"/>
     </row>
-    <row r="168" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D168" s="6"/>
     </row>
-    <row r="169" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D169" s="6"/>
     </row>
-    <row r="170" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D170" s="6"/>
     </row>
-    <row r="171" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D171" s="6"/>
     </row>
-    <row r="172" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D172" s="6"/>
     </row>
-    <row r="173" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D173" s="6"/>
     </row>
-    <row r="174" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D174" s="6"/>
     </row>
-    <row r="175" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D175" s="6"/>
     </row>
-    <row r="176" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D176" s="6"/>
     </row>
-    <row r="177" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D177" s="6"/>
     </row>
-    <row r="178" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D178" s="6"/>
     </row>
-    <row r="179" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D179" s="6"/>
     </row>
-    <row r="180" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D180" s="6"/>
     </row>
-    <row r="181" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D181" s="6"/>
     </row>
-    <row r="182" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D182" s="6"/>
     </row>
-    <row r="183" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D183" s="6"/>
     </row>
-    <row r="184" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D184" s="6"/>
     </row>
-    <row r="185" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D185" s="6"/>
     </row>
-    <row r="186" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D186" s="6"/>
     </row>
-    <row r="187" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D187" s="6"/>
     </row>
-    <row r="188" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D188" s="6"/>
     </row>
-    <row r="189" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="189" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D189" s="6"/>
     </row>
-    <row r="190" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D190" s="6"/>
     </row>
-    <row r="191" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D191" s="6"/>
     </row>
-    <row r="192" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="192" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D192" s="6"/>
     </row>
-    <row r="193" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D193" s="6"/>
       <c r="H193" s="6"/>
     </row>
-    <row r="194" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D194" s="6"/>
     </row>
-    <row r="195" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D195" s="6"/>
     </row>
-    <row r="196" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D196" s="6"/>
     </row>
-    <row r="197" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D197" s="6"/>
     </row>
-    <row r="198" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D198" s="6"/>
     </row>
-    <row r="199" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="199" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D199" s="6"/>
     </row>
-    <row r="200" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D200" s="6"/>
     </row>
-    <row r="201" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D201" s="6"/>
     </row>
-    <row r="202" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="202" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D202" s="6"/>
     </row>
-    <row r="203" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D203" s="6"/>
     </row>
-    <row r="204" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D204" s="6"/>
     </row>
-    <row r="205" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="205" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D205" s="6"/>
     </row>
-    <row r="206" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="206" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D206" s="6"/>
     </row>
-    <row r="207" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="207" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D207" s="6"/>
     </row>
-    <row r="208" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="208" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D208" s="6"/>
     </row>
-    <row r="209" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="209" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D209" s="6"/>
     </row>
-    <row r="210" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="210" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D210" s="6"/>
     </row>
-    <row r="211" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="211" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D211" s="6"/>
     </row>
-    <row r="212" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="212" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D212" s="6"/>
     </row>
-    <row r="213" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="213" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D213" s="6"/>
     </row>
-    <row r="214" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="214" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D214" s="6"/>
     </row>
-    <row r="215" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="215" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D215" s="6"/>
     </row>
-    <row r="216" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="216" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D216" s="6"/>
     </row>
-    <row r="217" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="217" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D217" s="6"/>
     </row>
-    <row r="218" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="218" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D218" s="6"/>
     </row>
-    <row r="219" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="219" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D219" s="6"/>
     </row>
-    <row r="220" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="220" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D220" s="6"/>
     </row>
-    <row r="221" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="221" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D221" s="6"/>
     </row>
-    <row r="222" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="222" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D222" s="6"/>
     </row>
-    <row r="223" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="223" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D223" s="6"/>
     </row>
-    <row r="224" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="224" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D224" s="6"/>
     </row>
-    <row r="225" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="225" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D225" s="6"/>
       <c r="H225" s="6"/>
     </row>
-    <row r="226" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="226" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D226" s="6"/>
     </row>
-    <row r="227" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="227" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D227" s="6"/>
     </row>
-    <row r="228" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="228" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D228" s="6"/>
     </row>
-    <row r="229" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="229" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D229" s="6"/>
     </row>
-    <row r="230" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="230" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D230" s="6"/>
     </row>
-    <row r="231" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="231" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D231" s="6"/>
     </row>
-    <row r="232" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="232" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D232" s="6"/>
     </row>
-    <row r="233" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="233" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D233" s="6"/>
     </row>
-    <row r="234" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="234" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D234" s="6"/>
     </row>
-    <row r="235" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="235" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D235" s="6"/>
     </row>
-    <row r="236" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="236" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D236" s="6"/>
     </row>
-    <row r="237" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="237" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D237" s="6"/>
     </row>
-    <row r="238" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="238" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D238" s="6"/>
     </row>
-    <row r="239" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="239" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D239" s="6"/>
     </row>
-    <row r="240" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="240" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D240" s="6"/>
     </row>
-    <row r="241" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="241" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D241" s="6"/>
     </row>
-    <row r="242" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="242" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D242" s="6"/>
     </row>
-    <row r="243" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="243" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D243" s="6"/>
     </row>
-    <row r="244" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="244" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D244" s="6"/>
     </row>
-    <row r="245" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="245" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D245" s="6"/>
     </row>
-    <row r="246" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="246" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D246" s="6"/>
     </row>
-    <row r="247" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="247" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D247" s="6"/>
     </row>
-    <row r="248" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="248" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D248" s="6"/>
     </row>
-    <row r="249" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="249" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D249" s="6"/>
     </row>
-    <row r="250" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="250" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D250" s="6"/>
     </row>
-    <row r="251" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="251" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D251" s="6"/>
     </row>
-    <row r="252" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="252" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D252" s="6"/>
     </row>
-    <row r="253" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="253" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D253" s="6"/>
     </row>
-    <row r="254" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="254" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D254" s="6"/>
     </row>
-    <row r="255" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="255" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D255" s="6"/>
     </row>
-    <row r="256" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="256" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D256" s="6"/>
     </row>
-    <row r="257" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="257" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D257" s="6"/>
       <c r="H257" s="6"/>
     </row>
-    <row r="258" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="258" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D258" s="6"/>
     </row>
-    <row r="259" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="259" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D259" s="6"/>
     </row>
-    <row r="260" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="260" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D260" s="6"/>
     </row>
-    <row r="261" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="261" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D261" s="6"/>
     </row>
-    <row r="262" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="262" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D262" s="6"/>
     </row>
-    <row r="263" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="263" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D263" s="6"/>
     </row>
-    <row r="264" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="264" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D264" s="6"/>
     </row>
-    <row r="265" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="265" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D265" s="6"/>
     </row>
-    <row r="266" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="266" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D266" s="6"/>
     </row>
-    <row r="267" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="267" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D267" s="6"/>
     </row>
-    <row r="268" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="268" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D268" s="6"/>
     </row>
-    <row r="269" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="269" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D269" s="6"/>
     </row>
-    <row r="270" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="270" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D270" s="6"/>
     </row>
-    <row r="271" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="271" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D271" s="6"/>
     </row>
-    <row r="272" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="272" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D272" s="6"/>
     </row>
-    <row r="273" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="273" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D273" s="6"/>
     </row>
-    <row r="274" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="274" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D274" s="6"/>
     </row>
-    <row r="275" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="275" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D275" s="6"/>
     </row>
-    <row r="276" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="276" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D276" s="6"/>
     </row>
-    <row r="277" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="277" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D277" s="6"/>
     </row>
-    <row r="278" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="278" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D278" s="6"/>
     </row>
-    <row r="279" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="279" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D279" s="6"/>
     </row>
-    <row r="280" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="280" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D280" s="6"/>
     </row>
-    <row r="281" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="281" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D281" s="6"/>
     </row>
-    <row r="282" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="282" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D282" s="6"/>
     </row>
-    <row r="283" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="283" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D283" s="6"/>
     </row>
-    <row r="284" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="284" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D284" s="6"/>
     </row>
-    <row r="285" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="285" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D285" s="6"/>
     </row>
-    <row r="286" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="286" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D286" s="6"/>
     </row>
-    <row r="287" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="287" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D287" s="6"/>
     </row>
-    <row r="288" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="288" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D288" s="6"/>
     </row>
-    <row r="289" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="289" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D289" s="6"/>
       <c r="H289" s="6"/>
     </row>
-    <row r="290" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="290" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D290" s="6"/>
       <c r="H290" s="6"/>
     </row>
-    <row r="291" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="291" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D291" s="6"/>
       <c r="H291" s="6"/>
     </row>
-    <row r="292" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="292" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D292" s="6"/>
       <c r="H292" s="6"/>
     </row>
-    <row r="293" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="293" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D293" s="6"/>
       <c r="H293" s="6"/>
     </row>
-    <row r="294" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="294" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D294" s="6"/>
       <c r="H294" s="6"/>
     </row>
-    <row r="295" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="295" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D295" s="6"/>
       <c r="H295" s="6"/>
     </row>
-    <row r="296" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="296" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D296" s="6"/>
       <c r="H296" s="6"/>
     </row>
-    <row r="297" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="297" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D297" s="6"/>
       <c r="H297" s="6"/>
     </row>
-    <row r="298" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="298" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D298" s="6"/>
       <c r="H298" s="6"/>
     </row>
-    <row r="299" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="299" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D299" s="6"/>
       <c r="H299" s="6"/>
     </row>
-    <row r="300" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="300" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D300" s="6"/>
       <c r="H300" s="6"/>
     </row>
-    <row r="301" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="301" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D301" s="6"/>
       <c r="H301" s="6"/>
     </row>
-    <row r="302" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="302" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D302" s="6"/>
       <c r="H302" s="6"/>
     </row>
-    <row r="303" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="303" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D303" s="6"/>
       <c r="H303" s="6"/>
     </row>
-    <row r="304" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="304" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D304" s="6"/>
       <c r="H304" s="6"/>
     </row>
-    <row r="305" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="305" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D305" s="6"/>
       <c r="H305" s="6"/>
     </row>
-    <row r="306" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="306" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D306" s="6"/>
       <c r="H306" s="6"/>
     </row>
-    <row r="307" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="307" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D307" s="6"/>
       <c r="H307" s="6"/>
     </row>
-    <row r="308" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="308" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D308" s="6"/>
       <c r="H308" s="6"/>
     </row>
-    <row r="309" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="309" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D309" s="6"/>
       <c r="H309" s="6"/>
     </row>
-    <row r="310" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="310" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D310" s="6"/>
       <c r="H310" s="6"/>
     </row>
-    <row r="311" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="311" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D311" s="6"/>
       <c r="H311" s="6"/>
     </row>
-    <row r="312" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="312" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D312" s="6"/>
       <c r="H312" s="6"/>
     </row>
-    <row r="313" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="313" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D313" s="6"/>
       <c r="H313" s="6"/>
     </row>
-    <row r="314" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="314" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D314" s="6"/>
       <c r="H314" s="6"/>
     </row>
-    <row r="315" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="315" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D315" s="6"/>
       <c r="H315" s="6"/>
     </row>
-    <row r="316" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="316" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D316" s="6"/>
       <c r="H316" s="6"/>
     </row>
-    <row r="317" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="317" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D317" s="6"/>
       <c r="H317" s="6"/>
     </row>
-    <row r="318" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="318" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D318" s="6"/>
       <c r="H318" s="6"/>
     </row>
-    <row r="319" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="319" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D319" s="6"/>
       <c r="H319" s="6"/>
     </row>
-    <row r="320" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="320" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D320" s="6"/>
       <c r="H320" s="6"/>
     </row>
-    <row r="321" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="321" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D321" s="6"/>
       <c r="H321" s="6"/>
     </row>
-    <row r="322" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="322" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D322" s="6"/>
       <c r="H322" s="6"/>
     </row>
-    <row r="323" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="323" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D323" s="6"/>
       <c r="H323" s="6"/>
     </row>
-    <row r="324" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="324" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D324" s="6"/>
       <c r="H324" s="6"/>
     </row>
-    <row r="325" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="325" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D325" s="6"/>
       <c r="H325" s="6"/>
     </row>
-    <row r="326" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="326" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D326" s="6"/>
       <c r="H326" s="6"/>
     </row>
-    <row r="327" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="327" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D327" s="6"/>
       <c r="H327" s="6"/>
     </row>
-    <row r="328" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="328" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D328" s="6"/>
       <c r="H328" s="6"/>
     </row>
-    <row r="329" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="329" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D329" s="6"/>
       <c r="H329" s="6"/>
     </row>
-    <row r="330" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="330" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D330" s="6"/>
       <c r="H330" s="6"/>
     </row>
-    <row r="331" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="331" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D331" s="6"/>
       <c r="H331" s="6"/>
     </row>
-    <row r="332" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="332" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D332" s="6"/>
       <c r="H332" s="6"/>
     </row>
-    <row r="333" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="333" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D333" s="6"/>
       <c r="H333" s="6"/>
     </row>
-    <row r="334" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="334" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D334" s="6"/>
       <c r="H334" s="6"/>
     </row>
-    <row r="335" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="335" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D335" s="6"/>
       <c r="H335" s="6"/>
     </row>
-    <row r="336" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="336" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D336" s="6"/>
       <c r="H336" s="6"/>
     </row>
-    <row r="337" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="337" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D337" s="6"/>
       <c r="H337" s="6"/>
     </row>
-    <row r="338" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="338" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D338" s="6"/>
       <c r="H338" s="6"/>
     </row>
-    <row r="339" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="339" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D339" s="6"/>
       <c r="H339" s="6"/>
     </row>
-    <row r="340" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="340" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D340" s="6"/>
       <c r="H340" s="6"/>
     </row>
-    <row r="341" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="341" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D341" s="6"/>
       <c r="H341" s="6"/>
     </row>
-    <row r="342" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="342" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D342" s="6"/>
       <c r="H342" s="6"/>
     </row>
-    <row r="343" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="343" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D343" s="6"/>
       <c r="H343" s="6"/>
     </row>
-    <row r="344" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="344" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D344" s="6"/>
       <c r="H344" s="6"/>
     </row>
-    <row r="345" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="345" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D345" s="6"/>
       <c r="H345" s="6"/>
     </row>
-    <row r="346" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="346" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D346" s="6"/>
       <c r="H346" s="6"/>
     </row>
-    <row r="347" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="347" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D347" s="6"/>
       <c r="H347" s="6"/>
     </row>
-    <row r="348" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="348" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D348" s="6"/>
       <c r="H348" s="6"/>
     </row>
-    <row r="349" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="349" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D349" s="6"/>
       <c r="H349" s="6"/>
     </row>
-    <row r="350" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="350" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D350" s="6"/>
       <c r="H350" s="6"/>
     </row>
-    <row r="351" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="351" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D351" s="6"/>
       <c r="H351" s="6"/>
     </row>
-    <row r="352" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="352" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D352" s="6"/>
       <c r="H352" s="6"/>
     </row>
-    <row r="353" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="353" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D353" s="6"/>
       <c r="H353" s="6"/>
     </row>
-    <row r="354" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="354" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D354" s="6"/>
       <c r="H354" s="6"/>
     </row>
-    <row r="355" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="355" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D355" s="6"/>
       <c r="H355" s="6"/>
     </row>
-    <row r="356" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="356" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D356" s="6"/>
       <c r="H356" s="6"/>
     </row>
-    <row r="357" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="357" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D357" s="6"/>
       <c r="H357" s="6"/>
     </row>
-    <row r="358" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="358" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D358" s="6"/>
       <c r="H358" s="6"/>
     </row>
-    <row r="359" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="359" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D359" s="6"/>
       <c r="H359" s="6"/>
     </row>
-    <row r="360" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="360" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D360" s="6"/>
       <c r="H360" s="6"/>
     </row>
-    <row r="361" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="361" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D361" s="6"/>
       <c r="H361" s="6"/>
     </row>
-    <row r="362" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="362" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D362" s="6"/>
       <c r="H362" s="6"/>
     </row>
-    <row r="363" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="363" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D363" s="6"/>
       <c r="H363" s="6"/>
     </row>
-    <row r="364" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="364" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D364" s="6"/>
       <c r="H364" s="6"/>
     </row>
-    <row r="365" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="365" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D365" s="6"/>
       <c r="H365" s="6"/>
     </row>
-    <row r="366" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="366" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D366" s="6"/>
       <c r="H366" s="6"/>
     </row>
-    <row r="367" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="367" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D367" s="6"/>
       <c r="H367" s="6"/>
     </row>
-    <row r="368" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="368" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D368" s="6"/>
       <c r="H368" s="6"/>
     </row>
-    <row r="369" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="369" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D369" s="6"/>
       <c r="H369" s="6"/>
     </row>
-    <row r="370" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="370" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D370" s="6"/>
       <c r="H370" s="6"/>
     </row>
-    <row r="371" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="371" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D371" s="6"/>
       <c r="H371" s="6"/>
     </row>
-    <row r="372" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="372" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D372" s="6"/>
       <c r="H372" s="6"/>
     </row>
-    <row r="373" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="373" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D373" s="6"/>
       <c r="H373" s="6"/>
     </row>
-    <row r="374" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="374" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D374" s="6"/>
       <c r="H374" s="6"/>
     </row>
-    <row r="375" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="375" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D375" s="6"/>
       <c r="H375" s="6"/>
     </row>
-    <row r="376" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="376" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D376" s="6"/>
       <c r="H376" s="6"/>
     </row>
-    <row r="377" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="377" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D377" s="6"/>
       <c r="H377" s="6"/>
     </row>
-    <row r="378" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="378" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D378" s="6"/>
       <c r="H378" s="6"/>
     </row>
-    <row r="379" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="379" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D379" s="6"/>
       <c r="H379" s="6"/>
     </row>
-    <row r="380" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="380" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D380" s="6"/>
       <c r="H380" s="6"/>
     </row>
-    <row r="381" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="381" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D381" s="6"/>
       <c r="H381" s="6"/>
     </row>
-    <row r="382" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="382" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D382" s="6"/>
       <c r="H382" s="6"/>
     </row>
-    <row r="383" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="383" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D383" s="6"/>
       <c r="H383" s="6"/>
     </row>
-    <row r="384" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="384" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D384" s="6"/>
       <c r="H384" s="6"/>
     </row>
-    <row r="385" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="385" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D385" s="6"/>
       <c r="H385" s="6"/>
     </row>
-    <row r="386" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="386" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D386" s="6"/>
       <c r="H386" s="6"/>
     </row>
-    <row r="387" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="387" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D387" s="6"/>
       <c r="H387" s="6"/>
     </row>
-    <row r="388" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="388" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D388" s="6"/>
       <c r="H388" s="6"/>
     </row>
-    <row r="389" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="389" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D389" s="6"/>
       <c r="H389" s="6"/>
     </row>
-    <row r="390" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="390" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D390" s="6"/>
       <c r="H390" s="6"/>
     </row>
-    <row r="391" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="391" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D391" s="6"/>
       <c r="H391" s="6"/>
     </row>
-    <row r="392" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="392" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D392" s="6"/>
       <c r="H392" s="6"/>
     </row>
-    <row r="393" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="393" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D393" s="6"/>
       <c r="H393" s="6"/>
     </row>
-    <row r="394" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="394" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D394" s="6"/>
       <c r="H394" s="6"/>
     </row>
-    <row r="395" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="395" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D395" s="6"/>
       <c r="H395" s="6"/>
     </row>
-    <row r="396" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="396" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D396" s="6"/>
       <c r="H396" s="6"/>
     </row>
-    <row r="397" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="397" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D397" s="6"/>
       <c r="H397" s="6"/>
     </row>
-    <row r="398" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="398" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D398" s="6"/>
       <c r="H398" s="6"/>
     </row>
-    <row r="399" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="399" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D399" s="6"/>
       <c r="H399" s="6"/>
     </row>
-    <row r="400" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="400" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D400" s="6"/>
       <c r="H400" s="6"/>
     </row>
-    <row r="401" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="401" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D401" s="6"/>
       <c r="H401" s="6"/>
     </row>
-    <row r="402" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="402" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D402" s="6"/>
       <c r="H402" s="6"/>
     </row>
-    <row r="403" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="403" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D403" s="6"/>
       <c r="H403" s="6"/>
     </row>
-    <row r="404" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="404" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D404" s="6"/>
       <c r="H404" s="6"/>
     </row>
-    <row r="405" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="405" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D405" s="6"/>
       <c r="H405" s="6"/>
     </row>
-    <row r="406" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="406" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D406" s="6"/>
       <c r="H406" s="6"/>
     </row>
-    <row r="407" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="407" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D407" s="6"/>
       <c r="H407" s="6"/>
     </row>
-    <row r="408" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="408" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D408" s="6"/>
       <c r="H408" s="6"/>
     </row>
-    <row r="409" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="409" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D409" s="6"/>
       <c r="H409" s="6"/>
     </row>
-    <row r="410" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="410" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D410" s="6"/>
       <c r="H410" s="6"/>
     </row>
-    <row r="411" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="411" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D411" s="6"/>
       <c r="H411" s="6"/>
     </row>
-    <row r="412" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="412" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D412" s="6"/>
       <c r="H412" s="6"/>
     </row>
-    <row r="413" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="413" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D413" s="6"/>
       <c r="H413" s="6"/>
     </row>
-    <row r="414" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="414" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D414" s="6"/>
       <c r="H414" s="6"/>
     </row>
-    <row r="415" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="415" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D415" s="6"/>
       <c r="H415" s="6"/>
     </row>
-    <row r="416" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="416" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D416" s="6"/>
       <c r="H416" s="6"/>
     </row>
-    <row r="417" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="417" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D417" s="6"/>
       <c r="H417" s="6"/>
     </row>
-    <row r="418" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="418" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D418" s="6"/>
       <c r="H418" s="6"/>
     </row>
-    <row r="419" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="419" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D419" s="6"/>
       <c r="H419" s="6"/>
     </row>
-    <row r="420" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="420" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D420" s="6"/>
       <c r="H420" s="6"/>
     </row>
-    <row r="421" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="421" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D421" s="6"/>
       <c r="H421" s="6"/>
     </row>
-    <row r="422" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="422" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D422" s="6"/>
       <c r="H422" s="6"/>
     </row>
-    <row r="423" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="423" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D423" s="6"/>
       <c r="H423" s="6"/>
     </row>
-    <row r="424" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="424" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D424" s="6"/>
       <c r="H424" s="6"/>
     </row>
-    <row r="425" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="425" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D425" s="6"/>
       <c r="H425" s="6"/>
     </row>
-    <row r="426" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="426" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D426" s="6"/>
       <c r="H426" s="6"/>
     </row>
-    <row r="427" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="427" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D427" s="6"/>
       <c r="H427" s="6"/>
     </row>
-    <row r="428" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="428" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D428" s="6"/>
       <c r="H428" s="6"/>
     </row>
-    <row r="429" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="429" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D429" s="6"/>
       <c r="H429" s="6"/>
     </row>
-    <row r="430" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="430" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D430" s="6"/>
       <c r="H430" s="6"/>
     </row>
-    <row r="431" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="431" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D431" s="6"/>
       <c r="H431" s="6"/>
     </row>
-    <row r="432" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="432" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D432" s="6"/>
       <c r="H432" s="6"/>
     </row>
-    <row r="433" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="433" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D433" s="6"/>
       <c r="H433" s="6"/>
     </row>
-    <row r="434" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="434" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D434" s="6"/>
       <c r="H434" s="6"/>
     </row>
-    <row r="435" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="435" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D435" s="6"/>
       <c r="H435" s="6"/>
     </row>
-    <row r="436" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="436" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D436" s="6"/>
       <c r="H436" s="6"/>
     </row>
-    <row r="437" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="437" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D437" s="6"/>
       <c r="H437" s="6"/>
     </row>
-    <row r="438" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="438" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D438" s="6"/>
       <c r="H438" s="6"/>
     </row>
-    <row r="439" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="439" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D439" s="6"/>
       <c r="H439" s="6"/>
     </row>
-    <row r="440" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="440" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D440" s="6"/>
       <c r="H440" s="6"/>
     </row>
-    <row r="441" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="441" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D441" s="6"/>
       <c r="H441" s="6"/>
     </row>
-    <row r="442" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="442" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D442" s="6"/>
       <c r="H442" s="6"/>
     </row>
-    <row r="443" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="443" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D443" s="6"/>
       <c r="H443" s="6"/>
     </row>
-    <row r="444" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="444" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D444" s="6"/>
       <c r="H444" s="6"/>
     </row>
-    <row r="445" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="445" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D445" s="6"/>
       <c r="H445" s="6"/>
     </row>
-    <row r="446" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="446" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D446" s="6"/>
       <c r="H446" s="6"/>
     </row>
-    <row r="447" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="447" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D447" s="6"/>
       <c r="H447" s="6"/>
     </row>
-    <row r="448" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="448" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D448" s="6"/>
       <c r="H448" s="6"/>
     </row>
-    <row r="449" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="449" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D449" s="6"/>
       <c r="H449" s="6"/>
     </row>
-    <row r="450" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="450" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D450" s="6"/>
       <c r="H450" s="6"/>
     </row>
-    <row r="451" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="451" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D451" s="6"/>
       <c r="H451" s="6"/>
     </row>
-    <row r="452" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="452" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D452" s="6"/>
       <c r="H452" s="6"/>
     </row>
-    <row r="453" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="453" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D453" s="6"/>
       <c r="H453" s="6"/>
     </row>
-    <row r="454" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="454" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D454" s="6"/>
       <c r="H454" s="6"/>
     </row>
-    <row r="455" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="455" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D455" s="6"/>
       <c r="H455" s="6"/>
     </row>
-    <row r="456" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="456" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D456" s="6"/>
       <c r="H456" s="6"/>
     </row>
-    <row r="457" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="457" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D457" s="6"/>
       <c r="H457" s="6"/>
     </row>
-    <row r="458" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="458" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D458" s="6"/>
       <c r="H458" s="6"/>
     </row>
-    <row r="459" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="459" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D459" s="6"/>
       <c r="H459" s="6"/>
     </row>
-    <row r="460" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="460" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D460" s="6"/>
       <c r="H460" s="6"/>
     </row>
-    <row r="461" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="461" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D461" s="6"/>
       <c r="H461" s="6"/>
     </row>
-    <row r="462" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="462" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D462" s="6"/>
       <c r="H462" s="6"/>
     </row>
-    <row r="463" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="463" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D463" s="6"/>
       <c r="H463" s="6"/>
     </row>
-    <row r="464" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="464" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D464" s="6"/>
       <c r="H464" s="6"/>
     </row>
-    <row r="465" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="465" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D465" s="6"/>
       <c r="H465" s="6"/>
     </row>
-    <row r="466" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="466" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D466" s="6"/>
       <c r="H466" s="6"/>
     </row>
-    <row r="467" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="467" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D467" s="6"/>
       <c r="H467" s="6"/>
     </row>
-    <row r="468" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="468" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D468" s="6"/>
       <c r="H468" s="6"/>
     </row>
-    <row r="469" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="469" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D469" s="6"/>
       <c r="H469" s="6"/>
     </row>
-    <row r="470" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="470" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D470" s="6"/>
       <c r="H470" s="6"/>
     </row>
-    <row r="471" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="471" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D471" s="6"/>
       <c r="H471" s="6"/>
     </row>
-    <row r="472" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="472" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D472" s="6"/>
       <c r="H472" s="6"/>
     </row>
-    <row r="473" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="473" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D473" s="6"/>
       <c r="H473" s="6"/>
     </row>
-    <row r="474" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="474" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D474" s="6"/>
       <c r="H474" s="6"/>
     </row>
-    <row r="475" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="475" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D475" s="6"/>
       <c r="H475" s="6"/>
     </row>
-    <row r="476" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="476" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D476" s="6"/>
       <c r="H476" s="6"/>
     </row>
-    <row r="477" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="477" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D477" s="6"/>
       <c r="H477" s="6"/>
     </row>
-    <row r="478" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="478" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D478" s="6"/>
       <c r="H478" s="6"/>
     </row>
-    <row r="479" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="479" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D479" s="6"/>
       <c r="H479" s="6"/>
     </row>
-    <row r="480" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="480" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D480" s="6"/>
       <c r="H480" s="6"/>
     </row>
-    <row r="481" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="481" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D481" s="6"/>
       <c r="H481" s="6"/>
     </row>
@@ -6936,9 +6936,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B5:M8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>21</v>
       </c>
@@ -6976,7 +6976,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="13">
         <v>43672</v>
       </c>
@@ -6999,7 +6999,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="13">
         <v>43684</v>
       </c>
@@ -7030,9 +7030,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:P3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>34</v>
       </c>
@@ -7079,7 +7079,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>19</v>
       </c>

--- a/IEF_Home/UploadedFiles/3_EI_VehicleArchetypes_Wolfram_2020_Test.xlsx
+++ b/IEF_Home/UploadedFiles/3_EI_VehicleArchetypes_Wolfram_2020_Test.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20415"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62DF037-8C73-442B-9EF6-5372DD20F6AC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFA6F8E-21AB-4B3B-A491-77EF449EEB0B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13425" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13698" windowHeight="5370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="5" r:id="rId1"/>
@@ -1068,12 +1068,24 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1085,6 +1097,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1097,6 +1112,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1113,9 +1131,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1128,6 +1152,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
@@ -1136,6 +1163,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1157,63 +1187,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1229,7 +1229,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1550,352 +1550,352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF917567-276E-40DD-8D48-0D1C387BC339}">
   <dimension ref="A1:Q72"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.15625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="7.140625" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.15625" customWidth="1"/>
+    <col min="2" max="2" width="15.83984375" customWidth="1"/>
+    <col min="3" max="3" width="23.15625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.83984375" customWidth="1"/>
+    <col min="5" max="5" width="11.68359375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.3125" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="3.28515625" customWidth="1"/>
+    <col min="9" max="9" width="24.83984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="3.3125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="E1" s="1"/>
       <c r="H1" s="10"/>
     </row>
-    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="80" t="s">
+    <row r="2" spans="1:17" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="B2" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="82"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="80" t="s">
+      <c r="F2" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="82"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="19"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="19" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="20"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="23" t="s">
         <v>107</v>
       </c>
       <c r="E3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="20">
         <v>1</v>
       </c>
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="26" t="s">
         <v>110</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="25"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="29"/>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="20">
         <v>2</v>
       </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="26" t="s">
+      <c r="B5" s="30"/>
+      <c r="C5" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="32" t="s">
         <v>196</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="28"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="30"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="35"/>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="20">
         <v>3</v>
       </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="26" t="s">
+      <c r="B6" s="36"/>
+      <c r="C6" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="32" t="s">
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="F6" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="G6" s="33" t="s">
+      <c r="G6" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="H6" s="34"/>
-      <c r="I6" s="35"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="40"/>
       <c r="L6" s="1"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="20">
         <v>4</v>
       </c>
-      <c r="B7" s="85" t="s">
+      <c r="B7" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="32" t="s">
         <v>114</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F7" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="G7" s="33" t="s">
+      <c r="G7" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="36"/>
-      <c r="I7" s="37"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="43"/>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="20">
         <v>5</v>
       </c>
-      <c r="B8" s="85"/>
-      <c r="C8" s="26" t="s">
+      <c r="B8" s="41"/>
+      <c r="C8" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="32">
         <v>3</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="F8" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="33" t="s">
+      <c r="G8" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="38"/>
-      <c r="I8" s="39"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="45"/>
       <c r="L8" s="1"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="20">
         <v>6</v>
       </c>
-      <c r="B9" s="85"/>
-      <c r="C9" s="26" t="s">
+      <c r="B9" s="41"/>
+      <c r="C9" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="32" t="s">
         <v>210</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="F9" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="G9" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="38"/>
-      <c r="I9" s="39"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="45"/>
       <c r="L9" s="1"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="20">
         <v>7</v>
       </c>
-      <c r="B10" s="85"/>
-      <c r="C10" s="26" t="s">
+      <c r="B10" s="41"/>
+      <c r="C10" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="D10" s="73" t="s">
+      <c r="D10" s="87" t="s">
         <v>210</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="40" t="s">
+      <c r="F10" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="G10" s="41" t="s">
+      <c r="G10" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="42" t="s">
+      <c r="H10" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="49">
         <v>48</v>
       </c>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="20">
         <v>8</v>
       </c>
-      <c r="B11" s="86" t="s">
+      <c r="B11" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="44" t="s">
+      <c r="C11" s="51" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="32" t="s">
         <v>211</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="32" t="s">
+      <c r="F11" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="45" t="s">
+      <c r="G11" s="52" t="s">
         <v>123</v>
       </c>
-      <c r="H11" s="45" t="s">
+      <c r="H11" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="46" t="s">
+      <c r="I11" s="53" t="s">
         <v>9</v>
       </c>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="20">
         <v>9</v>
       </c>
-      <c r="B12" s="87"/>
-      <c r="C12" s="47" t="s">
+      <c r="B12" s="54"/>
+      <c r="C12" s="55" t="s">
         <v>124</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="32" t="s">
         <v>212</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="48" t="s">
+      <c r="F12" s="56" t="s">
         <v>125</v>
       </c>
-      <c r="G12" s="49">
+      <c r="G12" s="57">
         <v>1</v>
       </c>
-      <c r="H12" s="50" t="s">
+      <c r="H12" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="51"/>
+      <c r="I12" s="59"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="20">
         <v>10</v>
       </c>
-      <c r="B13" s="87"/>
-      <c r="C13" s="47" t="s">
+      <c r="B13" s="54"/>
+      <c r="C13" s="55" t="s">
         <v>126</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="32" t="s">
         <v>202</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F13" s="48" t="s">
+      <c r="F13" s="56" t="s">
         <v>127</v>
       </c>
-      <c r="G13" s="49">
+      <c r="G13" s="57">
         <v>1</v>
       </c>
-      <c r="H13" s="50" t="s">
+      <c r="H13" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="I13" s="51"/>
+      <c r="I13" s="59"/>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="20">
         <v>11</v>
       </c>
-      <c r="B14" s="87"/>
-      <c r="C14" s="47" t="s">
+      <c r="B14" s="54"/>
+      <c r="C14" s="55" t="s">
         <v>129</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="32" t="s">
         <v>203</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="48" t="s">
+      <c r="F14" s="56" t="s">
         <v>130</v>
       </c>
-      <c r="G14" s="49">
+      <c r="G14" s="57">
         <v>1</v>
       </c>
-      <c r="H14" s="50" t="s">
+      <c r="H14" s="58" t="s">
         <v>131</v>
       </c>
-      <c r="I14" s="51"/>
+      <c r="I14" s="59"/>
       <c r="L14" s="1"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="20">
         <v>12</v>
       </c>
-      <c r="B15" s="87"/>
-      <c r="C15" s="47" t="s">
+      <c r="B15" s="54"/>
+      <c r="C15" s="55" t="s">
         <v>132</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="32" t="s">
         <v>4</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F15" s="48" t="s">
+      <c r="F15" s="56" t="s">
         <v>133</v>
       </c>
-      <c r="G15" s="49">
+      <c r="G15" s="57">
         <v>1</v>
       </c>
-      <c r="H15" s="50" t="s">
+      <c r="H15" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="51"/>
+      <c r="I15" s="59"/>
       <c r="L15" s="1"/>
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
@@ -1903,26 +1903,26 @@
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="20">
         <v>13</v>
       </c>
-      <c r="B16" s="87"/>
-      <c r="C16" s="47" t="s">
+      <c r="B16" s="54"/>
+      <c r="C16" s="55" t="s">
         <v>134</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="32" t="s">
         <v>4</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F16" s="52"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="50" t="s">
+      <c r="F16" s="60"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="I16" s="51"/>
+      <c r="I16" s="59"/>
       <c r="L16" s="1"/>
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
@@ -1930,24 +1930,24 @@
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="20">
         <v>14</v>
       </c>
-      <c r="B17" s="87"/>
-      <c r="C17" s="47" t="s">
+      <c r="B17" s="54"/>
+      <c r="C17" s="55" t="s">
         <v>135</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="32" t="s">
         <v>204</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F17" s="53"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="30"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="62"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="35"/>
       <c r="L17" s="1"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
@@ -1955,24 +1955,24 @@
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="17">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="20">
         <v>15</v>
       </c>
-      <c r="B18" s="87"/>
-      <c r="C18" s="47" t="s">
+      <c r="B18" s="54"/>
+      <c r="C18" s="55" t="s">
         <v>136</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="32" t="s">
         <v>205</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F18" s="53"/>
+      <c r="F18" s="61"/>
       <c r="G18" s="11"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="30"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="35"/>
       <c r="L18" s="1"/>
       <c r="M18" s="8"/>
       <c r="N18" s="8"/>
@@ -1980,24 +1980,24 @@
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="17">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="20">
         <v>16</v>
       </c>
-      <c r="B19" s="87"/>
-      <c r="C19" s="47" t="s">
+      <c r="B19" s="54"/>
+      <c r="C19" s="55" t="s">
         <v>137</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="32" t="s">
         <v>206</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F19" s="53"/>
+      <c r="F19" s="61"/>
       <c r="G19" s="11"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="30"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="35"/>
       <c r="L19" s="1"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
@@ -2005,24 +2005,24 @@
       <c r="P19" s="8"/>
       <c r="Q19" s="8"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="17">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="20">
         <v>17</v>
       </c>
-      <c r="B20" s="87"/>
-      <c r="C20" s="47" t="s">
+      <c r="B20" s="54"/>
+      <c r="C20" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="32" t="s">
         <v>207</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F20" s="28"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="30"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="35"/>
       <c r="L20" s="1"/>
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
@@ -2030,26 +2030,26 @@
       <c r="P20" s="8"/>
       <c r="Q20" s="8"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="17">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="20">
         <v>18</v>
       </c>
-      <c r="B21" s="88" t="s">
+      <c r="B21" s="63" t="s">
         <v>139</v>
       </c>
-      <c r="C21" s="47" t="s">
+      <c r="C21" s="55" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="32" t="s">
         <v>213</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F21" s="55"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="57"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="66"/>
       <c r="L21" s="1"/>
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
@@ -2057,15 +2057,15 @@
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="17">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="20">
         <v>19</v>
       </c>
-      <c r="B22" s="88"/>
-      <c r="C22" s="47" t="s">
+      <c r="B22" s="63"/>
+      <c r="C22" s="55" t="s">
         <v>141</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="32" t="s">
         <v>214</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -2080,15 +2080,15 @@
       <c r="P22" s="8"/>
       <c r="Q22" s="8"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="17">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="20">
         <v>20</v>
       </c>
-      <c r="B23" s="88"/>
-      <c r="C23" s="44" t="s">
+      <c r="B23" s="63"/>
+      <c r="C23" s="51" t="s">
         <v>142</v>
       </c>
-      <c r="D23" s="27" t="s">
+      <c r="D23" s="32" t="s">
         <v>208</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -2100,20 +2100,20 @@
       <c r="I23" s="8"/>
       <c r="L23" s="1"/>
       <c r="M23" s="8"/>
-      <c r="N23" s="58"/>
+      <c r="N23" s="67"/>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="17">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="20">
         <v>21</v>
       </c>
-      <c r="B24" s="88"/>
-      <c r="C24" s="44" t="s">
+      <c r="B24" s="63"/>
+      <c r="C24" s="51" t="s">
         <v>143</v>
       </c>
-      <c r="D24" s="59">
+      <c r="D24" s="68">
         <v>48</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -2130,22 +2130,22 @@
       <c r="P24" s="8"/>
       <c r="Q24" s="8"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="17">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="20">
         <v>22</v>
       </c>
-      <c r="B25" s="88"/>
-      <c r="C25" s="47" t="s">
+      <c r="B25" s="63"/>
+      <c r="C25" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="27" t="s">
+      <c r="D25" s="32" t="s">
         <v>209</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F25" s="8"/>
-      <c r="G25" s="58"/>
+      <c r="G25" s="67"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
       <c r="L25" s="1"/>
@@ -2155,17 +2155,17 @@
       <c r="P25" s="8"/>
       <c r="Q25" s="8"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="17">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="20">
         <v>23</v>
       </c>
-      <c r="B26" s="75" t="s">
+      <c r="B26" s="69" t="s">
         <v>144</v>
       </c>
-      <c r="C26" s="60" t="s">
+      <c r="C26" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="D26" s="61" t="s">
+      <c r="D26" s="71" t="s">
         <v>127</v>
       </c>
       <c r="E26" s="1" t="s">
@@ -2182,15 +2182,15 @@
       <c r="P26" s="8"/>
       <c r="Q26" s="8"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="17">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="20">
         <v>24</v>
       </c>
-      <c r="B27" s="75"/>
-      <c r="C27" s="60" t="s">
+      <c r="B27" s="69"/>
+      <c r="C27" s="70" t="s">
         <v>146</v>
       </c>
-      <c r="D27" s="61">
+      <c r="D27" s="71">
         <v>7</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -2209,15 +2209,15 @@
       <c r="P27" s="8"/>
       <c r="Q27" s="8"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="17">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="20">
         <v>25</v>
       </c>
-      <c r="B28" s="75"/>
-      <c r="C28" s="60" t="s">
+      <c r="B28" s="69"/>
+      <c r="C28" s="70" t="s">
         <v>147</v>
       </c>
-      <c r="D28" s="61" t="s">
+      <c r="D28" s="71" t="s">
         <v>133</v>
       </c>
       <c r="E28" s="1" t="s">
@@ -2236,15 +2236,15 @@
       <c r="P28" s="8"/>
       <c r="Q28" s="8"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="17">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="20">
         <v>26</v>
       </c>
-      <c r="B29" s="75"/>
-      <c r="C29" s="60" t="s">
+      <c r="B29" s="69"/>
+      <c r="C29" s="70" t="s">
         <v>148</v>
       </c>
-      <c r="D29" s="61">
+      <c r="D29" s="71">
         <v>2</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -2263,15 +2263,15 @@
       <c r="P29" s="8"/>
       <c r="Q29" s="8"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="17">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="20">
         <v>27</v>
       </c>
-      <c r="B30" s="75"/>
-      <c r="C30" s="60" t="s">
+      <c r="B30" s="69"/>
+      <c r="C30" s="70" t="s">
         <v>149</v>
       </c>
-      <c r="D30" s="61" t="s">
+      <c r="D30" s="71" t="s">
         <v>218</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -2290,15 +2290,15 @@
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="17">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="20">
         <v>28</v>
       </c>
-      <c r="B31" s="75"/>
-      <c r="C31" s="60" t="s">
+      <c r="B31" s="69"/>
+      <c r="C31" s="70" t="s">
         <v>150</v>
       </c>
-      <c r="D31" s="61">
+      <c r="D31" s="71">
         <v>14</v>
       </c>
       <c r="E31" s="1" t="s">
@@ -2317,12 +2317,12 @@
       <c r="P31" s="8"/>
       <c r="Q31" s="8"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="17">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="20">
         <v>29</v>
       </c>
-      <c r="B32" s="75"/>
-      <c r="C32" s="60" t="s">
+      <c r="B32" s="69"/>
+      <c r="C32" s="70" t="s">
         <v>151</v>
       </c>
       <c r="D32" s="6" t="s">
@@ -2344,15 +2344,15 @@
       <c r="P32" s="8"/>
       <c r="Q32" s="8"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="17">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="20">
         <v>30</v>
       </c>
-      <c r="B33" s="75"/>
-      <c r="C33" s="60" t="s">
+      <c r="B33" s="69"/>
+      <c r="C33" s="70" t="s">
         <v>152</v>
       </c>
-      <c r="D33" s="61">
+      <c r="D33" s="71">
         <v>10</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -2367,19 +2367,19 @@
       <c r="L33" s="8"/>
       <c r="M33" s="8"/>
       <c r="N33" s="3"/>
-      <c r="O33" s="63"/>
+      <c r="O33" s="73"/>
       <c r="P33" s="8"/>
       <c r="Q33" s="8"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="17">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="20">
         <v>31</v>
       </c>
-      <c r="B34" s="75"/>
-      <c r="C34" s="60" t="s">
+      <c r="B34" s="69"/>
+      <c r="C34" s="70" t="s">
         <v>153</v>
       </c>
-      <c r="D34" s="62" t="s">
+      <c r="D34" s="72" t="s">
         <v>4</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -2394,19 +2394,19 @@
       <c r="L34" s="8"/>
       <c r="M34" s="8"/>
       <c r="N34" s="3"/>
-      <c r="O34" s="63"/>
+      <c r="O34" s="73"/>
       <c r="P34" s="8"/>
       <c r="Q34" s="8"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" s="17">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="20">
         <v>32</v>
       </c>
-      <c r="B35" s="75"/>
-      <c r="C35" s="60" t="s">
+      <c r="B35" s="69"/>
+      <c r="C35" s="70" t="s">
         <v>154</v>
       </c>
-      <c r="D35" s="62" t="s">
+      <c r="D35" s="72" t="s">
         <v>4</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="F35" s="8"/>
       <c r="G35" s="3"/>
-      <c r="H35" s="63"/>
+      <c r="H35" s="73"/>
       <c r="I35" s="8"/>
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
@@ -2425,15 +2425,15 @@
       <c r="P35" s="8"/>
       <c r="Q35" s="8"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="17">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="20">
         <v>33</v>
       </c>
-      <c r="B36" s="75"/>
-      <c r="C36" s="60" t="s">
+      <c r="B36" s="69"/>
+      <c r="C36" s="70" t="s">
         <v>155</v>
       </c>
-      <c r="D36" s="61" t="s">
+      <c r="D36" s="71" t="s">
         <v>4</v>
       </c>
       <c r="E36" s="1" t="s">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F36" s="8"/>
       <c r="G36" s="3"/>
-      <c r="H36" s="63"/>
+      <c r="H36" s="73"/>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
@@ -2452,15 +2452,15 @@
       <c r="P36" s="8"/>
       <c r="Q36" s="8"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" s="17">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="20">
         <v>34</v>
       </c>
-      <c r="B37" s="75"/>
-      <c r="C37" s="60" t="s">
+      <c r="B37" s="69"/>
+      <c r="C37" s="70" t="s">
         <v>156</v>
       </c>
-      <c r="D37" s="61" t="s">
+      <c r="D37" s="71" t="s">
         <v>4</v>
       </c>
       <c r="E37" s="1" t="s">
@@ -2476,15 +2476,15 @@
       <c r="P37" s="8"/>
       <c r="Q37" s="8"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" s="17">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="20">
         <v>35</v>
       </c>
-      <c r="B38" s="75"/>
-      <c r="C38" s="60" t="s">
+      <c r="B38" s="69"/>
+      <c r="C38" s="70" t="s">
         <v>157</v>
       </c>
-      <c r="D38" s="61" t="s">
+      <c r="D38" s="71" t="s">
         <v>4</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -2500,15 +2500,15 @@
       <c r="P38" s="8"/>
       <c r="Q38" s="8"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" s="17">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="20">
         <v>36</v>
       </c>
-      <c r="B39" s="75"/>
-      <c r="C39" s="60" t="s">
+      <c r="B39" s="69"/>
+      <c r="C39" s="70" t="s">
         <v>158</v>
       </c>
-      <c r="D39" s="61" t="s">
+      <c r="D39" s="71" t="s">
         <v>4</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -2524,15 +2524,15 @@
       <c r="P39" s="8"/>
       <c r="Q39" s="8"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" s="17">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="20">
         <v>37</v>
       </c>
-      <c r="B40" s="75"/>
-      <c r="C40" s="60" t="s">
+      <c r="B40" s="69"/>
+      <c r="C40" s="70" t="s">
         <v>159</v>
       </c>
-      <c r="D40" s="61" t="s">
+      <c r="D40" s="71" t="s">
         <v>4</v>
       </c>
       <c r="E40" s="1" t="s">
@@ -2548,15 +2548,15 @@
       <c r="P40" s="8"/>
       <c r="Q40" s="8"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" s="17">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="20">
         <v>38</v>
       </c>
-      <c r="B41" s="75"/>
-      <c r="C41" s="60" t="s">
+      <c r="B41" s="69"/>
+      <c r="C41" s="70" t="s">
         <v>160</v>
       </c>
-      <c r="D41" s="61" t="s">
+      <c r="D41" s="71" t="s">
         <v>4</v>
       </c>
       <c r="E41" s="1" t="s">
@@ -2572,15 +2572,15 @@
       <c r="P41" s="8"/>
       <c r="Q41" s="8"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" s="17">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="20">
         <v>39</v>
       </c>
-      <c r="B42" s="75"/>
-      <c r="C42" s="60" t="s">
+      <c r="B42" s="69"/>
+      <c r="C42" s="70" t="s">
         <v>161</v>
       </c>
-      <c r="D42" s="61" t="s">
+      <c r="D42" s="71" t="s">
         <v>4</v>
       </c>
       <c r="E42" s="1" t="s">
@@ -2596,15 +2596,15 @@
       <c r="P42" s="8"/>
       <c r="Q42" s="8"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="17">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="20">
         <v>40</v>
       </c>
-      <c r="B43" s="75"/>
-      <c r="C43" s="60" t="s">
+      <c r="B43" s="69"/>
+      <c r="C43" s="70" t="s">
         <v>162</v>
       </c>
-      <c r="D43" s="61" t="s">
+      <c r="D43" s="71" t="s">
         <v>4</v>
       </c>
       <c r="E43" s="1" t="s">
@@ -2616,19 +2616,19 @@
       <c r="I43" s="8"/>
       <c r="M43" s="8"/>
       <c r="N43" s="3"/>
-      <c r="O43" s="58"/>
-      <c r="P43" s="64"/>
-      <c r="Q43" s="65"/>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="17">
+      <c r="O43" s="67"/>
+      <c r="P43" s="74"/>
+      <c r="Q43" s="75"/>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="20">
         <v>41</v>
       </c>
-      <c r="B44" s="75"/>
-      <c r="C44" s="60" t="s">
+      <c r="B44" s="69"/>
+      <c r="C44" s="70" t="s">
         <v>163</v>
       </c>
-      <c r="D44" s="61" t="s">
+      <c r="D44" s="71" t="s">
         <v>4</v>
       </c>
       <c r="E44" s="1" t="s">
@@ -2644,15 +2644,15 @@
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" s="17">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="20">
         <v>42</v>
       </c>
-      <c r="B45" s="75"/>
-      <c r="C45" s="60" t="s">
+      <c r="B45" s="69"/>
+      <c r="C45" s="70" t="s">
         <v>164</v>
       </c>
-      <c r="D45" s="61" t="s">
+      <c r="D45" s="71" t="s">
         <v>4</v>
       </c>
       <c r="E45" s="1" t="s">
@@ -2660,23 +2660,23 @@
       </c>
       <c r="F45" s="8"/>
       <c r="G45" s="3"/>
-      <c r="H45" s="58"/>
-      <c r="I45" s="64"/>
+      <c r="H45" s="67"/>
+      <c r="I45" s="74"/>
       <c r="M45" s="8"/>
       <c r="N45" s="7"/>
-      <c r="O45" s="49"/>
+      <c r="O45" s="57"/>
       <c r="P45" s="7"/>
-      <c r="Q45" s="63"/>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" s="17">
+      <c r="Q45" s="73"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="20">
         <v>43</v>
       </c>
-      <c r="B46" s="75"/>
-      <c r="C46" s="60" t="s">
+      <c r="B46" s="69"/>
+      <c r="C46" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="D46" s="61" t="s">
+      <c r="D46" s="71" t="s">
         <v>4</v>
       </c>
       <c r="E46" s="1" t="s">
@@ -2688,19 +2688,19 @@
       <c r="I46" s="3"/>
       <c r="M46" s="8"/>
       <c r="N46" s="7"/>
-      <c r="O46" s="49"/>
+      <c r="O46" s="57"/>
       <c r="P46" s="7"/>
-      <c r="Q46" s="63"/>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="17">
+      <c r="Q46" s="73"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="20">
         <v>44</v>
       </c>
-      <c r="B47" s="75"/>
-      <c r="C47" s="60" t="s">
+      <c r="B47" s="69"/>
+      <c r="C47" s="70" t="s">
         <v>166</v>
       </c>
-      <c r="D47" s="61" t="s">
+      <c r="D47" s="71" t="s">
         <v>4</v>
       </c>
       <c r="E47" s="1" t="s">
@@ -2708,23 +2708,23 @@
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="7"/>
-      <c r="H47" s="66"/>
+      <c r="H47" s="76"/>
       <c r="I47" s="7"/>
       <c r="M47" s="8"/>
       <c r="N47" s="10"/>
-      <c r="O47" s="49"/>
+      <c r="O47" s="57"/>
       <c r="P47" s="7"/>
-      <c r="Q47" s="63"/>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="17">
+      <c r="Q47" s="73"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="20">
         <v>45</v>
       </c>
-      <c r="B48" s="75"/>
-      <c r="C48" s="60" t="s">
+      <c r="B48" s="69"/>
+      <c r="C48" s="70" t="s">
         <v>167</v>
       </c>
-      <c r="D48" s="61" t="s">
+      <c r="D48" s="71" t="s">
         <v>4</v>
       </c>
       <c r="E48" s="1" t="s">
@@ -2732,23 +2732,23 @@
       </c>
       <c r="F48" s="8"/>
       <c r="G48" s="7"/>
-      <c r="H48" s="49"/>
+      <c r="H48" s="57"/>
       <c r="I48" s="7"/>
       <c r="M48" s="8"/>
       <c r="N48" s="10"/>
-      <c r="O48" s="49"/>
+      <c r="O48" s="57"/>
       <c r="P48" s="7"/>
-      <c r="Q48" s="63"/>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="17">
+      <c r="Q48" s="73"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="20">
         <v>46</v>
       </c>
-      <c r="B49" s="75"/>
-      <c r="C49" s="60" t="s">
+      <c r="B49" s="69"/>
+      <c r="C49" s="70" t="s">
         <v>168</v>
       </c>
-      <c r="D49" s="61" t="s">
+      <c r="D49" s="71" t="s">
         <v>4</v>
       </c>
       <c r="E49" s="1" t="s">
@@ -2756,23 +2756,23 @@
       </c>
       <c r="F49" s="8"/>
       <c r="G49" s="10"/>
-      <c r="H49" s="49"/>
+      <c r="H49" s="57"/>
       <c r="I49" s="7"/>
       <c r="M49" s="8"/>
       <c r="N49" s="8"/>
       <c r="O49" s="8"/>
       <c r="P49" s="7"/>
-      <c r="Q49" s="63"/>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50" s="17">
+      <c r="Q49" s="73"/>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="20">
         <v>47</v>
       </c>
-      <c r="B50" s="75"/>
-      <c r="C50" s="44" t="s">
+      <c r="B50" s="69"/>
+      <c r="C50" s="51" t="s">
         <v>169</v>
       </c>
-      <c r="D50" s="27" t="s">
+      <c r="D50" s="32" t="s">
         <v>221</v>
       </c>
       <c r="E50" s="1" t="s">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F50" s="8"/>
       <c r="G50" s="7"/>
-      <c r="H50" s="67"/>
+      <c r="H50" s="77"/>
       <c r="I50" s="7"/>
       <c r="M50" s="8"/>
       <c r="N50" s="8"/>
@@ -2788,15 +2788,15 @@
       <c r="P50" s="8"/>
       <c r="Q50" s="8"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="20">
         <v>48</v>
       </c>
-      <c r="B51" s="75"/>
-      <c r="C51" s="44" t="s">
+      <c r="B51" s="69"/>
+      <c r="C51" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="D51" s="27" t="s">
+      <c r="D51" s="32" t="s">
         <v>222</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
-      <c r="H51" s="67"/>
+      <c r="H51" s="77"/>
       <c r="I51" s="7"/>
       <c r="M51" s="8"/>
       <c r="N51" s="8"/>
@@ -2812,15 +2812,15 @@
       <c r="P51" s="8"/>
       <c r="Q51" s="8"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A52" s="17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="20">
         <v>49</v>
       </c>
-      <c r="B52" s="75"/>
-      <c r="C52" s="44" t="s">
+      <c r="B52" s="69"/>
+      <c r="C52" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="D52" s="27" t="s">
+      <c r="D52" s="32" t="s">
         <v>223</v>
       </c>
       <c r="E52" s="1" t="s">
@@ -2828,20 +2828,20 @@
       </c>
       <c r="F52" s="8"/>
       <c r="G52" s="8"/>
-      <c r="H52" s="67"/>
+      <c r="H52" s="77"/>
       <c r="I52" s="8"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53" s="17">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="20">
         <v>50</v>
       </c>
-      <c r="B53" s="76" t="s">
+      <c r="B53" s="78" t="s">
         <v>172</v>
       </c>
-      <c r="C53" s="26" t="s">
+      <c r="C53" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="D53" s="59" t="s">
+      <c r="D53" s="68" t="s">
         <v>198</v>
       </c>
       <c r="E53" s="1" t="s">
@@ -2852,15 +2852,15 @@
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="17">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="20">
         <v>51</v>
       </c>
-      <c r="B54" s="76"/>
-      <c r="C54" s="26" t="s">
+      <c r="B54" s="78"/>
+      <c r="C54" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="D54" s="27" t="s">
+      <c r="D54" s="32" t="s">
         <v>199</v>
       </c>
       <c r="E54" s="1" t="s">
@@ -2870,15 +2870,15 @@
       <c r="H54" s="8"/>
       <c r="I54" s="8"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A55" s="17">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="20">
         <v>52</v>
       </c>
-      <c r="B55" s="76"/>
-      <c r="C55" s="68" t="s">
+      <c r="B55" s="78"/>
+      <c r="C55" s="79" t="s">
         <v>175</v>
       </c>
-      <c r="D55" s="27" t="s">
+      <c r="D55" s="32" t="s">
         <v>200</v>
       </c>
       <c r="E55" s="1" t="s">
@@ -2888,261 +2888,261 @@
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="17">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="20">
         <v>53</v>
       </c>
-      <c r="B56" s="76"/>
-      <c r="C56" s="68" t="s">
+      <c r="B56" s="78"/>
+      <c r="C56" s="79" t="s">
         <v>176</v>
       </c>
-      <c r="D56" s="27" t="s">
+      <c r="D56" s="32" t="s">
         <v>4</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57" s="17">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="20">
         <v>54</v>
       </c>
-      <c r="B57" s="76"/>
-      <c r="C57" s="47" t="s">
+      <c r="B57" s="78"/>
+      <c r="C57" s="55" t="s">
         <v>177</v>
       </c>
-      <c r="D57" s="27" t="s">
+      <c r="D57" s="32" t="s">
         <v>178</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A58" s="17">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="20">
         <v>55</v>
       </c>
-      <c r="B58" s="76"/>
-      <c r="C58" s="68" t="s">
+      <c r="B58" s="78"/>
+      <c r="C58" s="79" t="s">
         <v>179</v>
       </c>
-      <c r="D58" s="27" t="s">
+      <c r="D58" s="32" t="s">
         <v>201</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A59" s="17">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="20">
         <v>56</v>
       </c>
-      <c r="B59" s="76"/>
-      <c r="C59" s="68" t="s">
+      <c r="B59" s="78"/>
+      <c r="C59" s="79" t="s">
         <v>180</v>
       </c>
-      <c r="D59" s="27" t="s">
+      <c r="D59" s="32" t="s">
         <v>201</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A60" s="17">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="20">
         <v>57</v>
       </c>
-      <c r="B60" s="76"/>
-      <c r="C60" s="26" t="s">
+      <c r="B60" s="78"/>
+      <c r="C60" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="D60" s="69">
+      <c r="D60" s="80">
         <v>1</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A61" s="17">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="20">
         <v>58</v>
       </c>
-      <c r="B61" s="77" t="s">
+      <c r="B61" s="81" t="s">
         <v>182</v>
       </c>
-      <c r="C61" s="68" t="s">
+      <c r="C61" s="79" t="s">
         <v>183</v>
       </c>
-      <c r="D61" s="70">
+      <c r="D61" s="82">
         <v>43684</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A62" s="17">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="20">
         <v>59</v>
       </c>
-      <c r="B62" s="77"/>
-      <c r="C62" s="68" t="s">
+      <c r="B62" s="81"/>
+      <c r="C62" s="79" t="s">
         <v>184</v>
       </c>
-      <c r="D62" s="70">
+      <c r="D62" s="82">
         <v>45602</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A63" s="17">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="20">
         <v>60</v>
       </c>
-      <c r="B63" s="77"/>
-      <c r="C63" s="68" t="s">
+      <c r="B63" s="81"/>
+      <c r="C63" s="79" t="s">
         <v>185</v>
       </c>
-      <c r="D63" s="27" t="s">
+      <c r="D63" s="32" t="s">
         <v>16</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A64" s="17">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="20">
         <v>61</v>
       </c>
-      <c r="B64" s="77"/>
-      <c r="C64" s="68" t="s">
+      <c r="B64" s="81"/>
+      <c r="C64" s="79" t="s">
         <v>186</v>
       </c>
-      <c r="D64" s="27" t="s">
+      <c r="D64" s="32" t="s">
         <v>197</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="17">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="20">
         <v>62</v>
       </c>
-      <c r="B65" s="77"/>
-      <c r="C65" s="26" t="s">
+      <c r="B65" s="81"/>
+      <c r="C65" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="D65" s="30"/>
+      <c r="D65" s="35"/>
       <c r="E65" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="17">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="20">
         <v>63</v>
       </c>
-      <c r="B66" s="77"/>
-      <c r="C66" s="26" t="s">
+      <c r="B66" s="81"/>
+      <c r="C66" s="31" t="s">
         <v>188</v>
       </c>
-      <c r="D66" s="30"/>
+      <c r="D66" s="35"/>
       <c r="E66" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="17">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="20">
         <v>64</v>
       </c>
-      <c r="B67" s="77"/>
-      <c r="C67" s="68" t="s">
+      <c r="B67" s="81"/>
+      <c r="C67" s="79" t="s">
         <v>189</v>
       </c>
-      <c r="D67" s="30"/>
+      <c r="D67" s="35"/>
       <c r="E67" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="17">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="20">
         <v>65</v>
       </c>
-      <c r="B68" s="78" t="s">
+      <c r="B68" s="83" t="s">
         <v>190</v>
       </c>
-      <c r="C68" s="71" t="s">
+      <c r="C68" s="84" t="s">
         <v>191</v>
       </c>
-      <c r="D68" s="30"/>
+      <c r="D68" s="35"/>
       <c r="E68" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="17">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="20">
         <v>66</v>
       </c>
-      <c r="B69" s="78"/>
-      <c r="C69" s="71" t="s">
+      <c r="B69" s="83"/>
+      <c r="C69" s="84" t="s">
         <v>192</v>
       </c>
-      <c r="D69" s="30"/>
+      <c r="D69" s="35"/>
       <c r="E69" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="17">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="20">
         <v>67</v>
       </c>
-      <c r="B70" s="78"/>
-      <c r="C70" s="71" t="s">
+      <c r="B70" s="83"/>
+      <c r="C70" s="84" t="s">
         <v>193</v>
       </c>
-      <c r="D70" s="30"/>
+      <c r="D70" s="35"/>
       <c r="E70" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="17">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="20">
         <v>68</v>
       </c>
-      <c r="B71" s="78"/>
-      <c r="C71" s="71" t="s">
+      <c r="B71" s="83"/>
+      <c r="C71" s="84" t="s">
         <v>194</v>
       </c>
-      <c r="D71" s="30"/>
+      <c r="D71" s="35"/>
       <c r="E71" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="17">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="20">
         <v>69</v>
       </c>
-      <c r="B72" s="79"/>
-      <c r="C72" s="72" t="s">
+      <c r="B72" s="85"/>
+      <c r="C72" s="86" t="s">
         <v>195</v>
       </c>
-      <c r="D72" s="57"/>
+      <c r="D72" s="66"/>
       <c r="E72" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B26:B52"/>
+    <mergeCell ref="B53:B60"/>
+    <mergeCell ref="B61:B67"/>
+    <mergeCell ref="B68:B72"/>
+    <mergeCell ref="B2:D2"/>
     <mergeCell ref="F2:I2"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B7:B10"/>
     <mergeCell ref="B11:B20"/>
     <mergeCell ref="B21:B25"/>
-    <mergeCell ref="B26:B52"/>
-    <mergeCell ref="B53:B60"/>
-    <mergeCell ref="B61:B67"/>
-    <mergeCell ref="B68:B72"/>
-    <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3151,35 +3151,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q481"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="33.140625" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" customWidth="1"/>
+    <col min="1" max="1" width="33.1015625" customWidth="1"/>
+    <col min="2" max="2" width="10.3125" customWidth="1"/>
+    <col min="3" max="3" width="13.05078125" customWidth="1"/>
+    <col min="4" max="4" width="22.05078125" customWidth="1"/>
+    <col min="5" max="5" width="11.68359375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.26171875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.26171875" customWidth="1"/>
     <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.42578125" customWidth="1"/>
-    <col min="10" max="10" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.41796875" customWidth="1"/>
+    <col min="10" max="10" width="35.578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.68359375" customWidth="1"/>
+    <col min="12" max="12" width="11.7890625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.9453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.41796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.68359375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.05078125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="88" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="88" t="s">
         <v>133</v>
       </c>
-      <c r="C1" s="74" t="s">
+      <c r="C1" s="88" t="s">
         <v>215</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -3201,7 +3201,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -3238,7 +3238,7 @@
         <v>217</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>219</v>
@@ -3259,7 +3259,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -3290,7 +3290,7 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>55</v>
       </c>
@@ -3321,7 +3321,7 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>56</v>
       </c>
@@ -3353,7 +3353,7 @@
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -3386,7 +3386,7 @@
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -3419,7 +3419,7 @@
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>59</v>
       </c>
@@ -3452,7 +3452,7 @@
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -3485,7 +3485,7 @@
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -3518,7 +3518,7 @@
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>62</v>
       </c>
@@ -3551,7 +3551,7 @@
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>63</v>
       </c>
@@ -3584,7 +3584,7 @@
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>64</v>
       </c>
@@ -3617,7 +3617,7 @@
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>65</v>
       </c>
@@ -3650,7 +3650,7 @@
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -3683,7 +3683,7 @@
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -3716,7 +3716,7 @@
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>68</v>
       </c>
@@ -3749,7 +3749,7 @@
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>69</v>
       </c>
@@ -3782,7 +3782,7 @@
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>70</v>
       </c>
@@ -3814,7 +3814,7 @@
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>71</v>
       </c>
@@ -3846,7 +3846,7 @@
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>72</v>
       </c>
@@ -3878,7 +3878,7 @@
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>73</v>
       </c>
@@ -3910,7 +3910,7 @@
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>74</v>
       </c>
@@ -3942,7 +3942,7 @@
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>75</v>
       </c>
@@ -3974,7 +3974,7 @@
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>76</v>
       </c>
@@ -4006,7 +4006,7 @@
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>77</v>
       </c>
@@ -4038,7 +4038,7 @@
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>78</v>
       </c>
@@ -4070,7 +4070,7 @@
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>79</v>
       </c>
@@ -4102,7 +4102,7 @@
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>80</v>
       </c>
@@ -4134,7 +4134,7 @@
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>81</v>
       </c>
@@ -4166,7 +4166,7 @@
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>82</v>
       </c>
@@ -4198,7 +4198,7 @@
       <c r="L32" s="6"/>
       <c r="M32" s="6"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>83</v>
       </c>
@@ -4230,7 +4230,7 @@
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>84</v>
       </c>
@@ -4263,7 +4263,7 @@
       <c r="M34" s="6"/>
       <c r="Q34" s="6"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>85</v>
       </c>
@@ -4296,7 +4296,7 @@
       <c r="M35" s="6"/>
       <c r="Q35" s="6"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>86</v>
       </c>
@@ -4329,7 +4329,7 @@
       <c r="M36" s="6"/>
       <c r="Q36" s="6"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>87</v>
       </c>
@@ -4362,7 +4362,7 @@
       <c r="M37" s="6"/>
       <c r="Q37" s="6"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>88</v>
       </c>
@@ -4395,7 +4395,7 @@
       <c r="M38" s="6"/>
       <c r="Q38" s="6"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>89</v>
       </c>
@@ -4428,7 +4428,7 @@
       <c r="M39" s="6"/>
       <c r="Q39" s="6"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -4462,7 +4462,7 @@
       <c r="N40" s="6"/>
       <c r="Q40" s="6"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -4496,7 +4496,7 @@
       <c r="N41" s="6"/>
       <c r="Q41" s="6"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>92</v>
       </c>
@@ -4530,7 +4530,7 @@
       <c r="N42" s="6"/>
       <c r="Q42" s="6"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>93</v>
       </c>
@@ -4564,7 +4564,7 @@
       <c r="N43" s="6"/>
       <c r="Q43" s="6"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>94</v>
       </c>
@@ -4598,7 +4598,7 @@
       <c r="N44" s="6"/>
       <c r="Q44" s="6"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>95</v>
       </c>
@@ -4632,7 +4632,7 @@
       <c r="N45" s="6"/>
       <c r="Q45" s="6"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>96</v>
       </c>
@@ -4664,7 +4664,7 @@
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>97</v>
       </c>
@@ -4696,7 +4696,7 @@
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>98</v>
       </c>
@@ -4728,7 +4728,7 @@
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>99</v>
       </c>
@@ -4760,7 +4760,7 @@
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
@@ -4770,7 +4770,7 @@
       <c r="N50" s="6"/>
       <c r="Q50" s="6"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
@@ -4778,7 +4778,7 @@
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
@@ -4787,7 +4787,7 @@
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="12"/>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
@@ -4799,7 +4799,7 @@
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="12"/>
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
@@ -4812,7 +4812,7 @@
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="12"/>
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
@@ -4824,7 +4824,7 @@
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="12"/>
       <c r="B56" s="12"/>
       <c r="C56" s="12"/>
@@ -4837,7 +4837,7 @@
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="12"/>
       <c r="B57" s="12"/>
       <c r="C57" s="12"/>
@@ -4849,7 +4849,7 @@
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="12"/>
       <c r="B58" s="12"/>
       <c r="C58" s="12"/>
@@ -4862,7 +4862,7 @@
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="12"/>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
@@ -4874,7 +4874,7 @@
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="12"/>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
@@ -4887,7 +4887,7 @@
       <c r="M60" s="6"/>
       <c r="N60" s="6"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="12"/>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
@@ -4899,7 +4899,7 @@
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="12"/>
       <c r="B62" s="12"/>
       <c r="C62" s="12"/>
@@ -4912,7 +4912,7 @@
       <c r="M62" s="6"/>
       <c r="N62" s="6"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="12"/>
       <c r="B63" s="12"/>
       <c r="C63" s="12"/>
@@ -4924,7 +4924,7 @@
       <c r="M63" s="6"/>
       <c r="N63" s="6"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="12"/>
       <c r="B64" s="12"/>
       <c r="C64" s="12"/>
@@ -4937,7 +4937,7 @@
       <c r="M64" s="6"/>
       <c r="N64" s="6"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="12"/>
       <c r="B65" s="12"/>
       <c r="C65" s="12"/>
@@ -4949,7 +4949,7 @@
       <c r="M65" s="6"/>
       <c r="N65" s="6"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="12"/>
       <c r="B66" s="12"/>
       <c r="C66" s="12"/>
@@ -4962,7 +4962,7 @@
       <c r="M66" s="6"/>
       <c r="N66" s="6"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="12"/>
       <c r="B67" s="12"/>
       <c r="C67" s="12"/>
@@ -4974,7 +4974,7 @@
       <c r="M67" s="6"/>
       <c r="N67" s="6"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="12"/>
       <c r="B68" s="12"/>
       <c r="C68" s="12"/>
@@ -4987,7 +4987,7 @@
       <c r="M68" s="6"/>
       <c r="N68" s="6"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="12"/>
       <c r="B69" s="12"/>
       <c r="C69" s="12"/>
@@ -4999,7 +4999,7 @@
       <c r="M69" s="6"/>
       <c r="N69" s="6"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="12"/>
       <c r="B70" s="12"/>
       <c r="C70" s="12"/>
@@ -5012,7 +5012,7 @@
       <c r="M70" s="6"/>
       <c r="N70" s="6"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="12"/>
       <c r="B71" s="12"/>
       <c r="C71" s="12"/>
@@ -5024,7 +5024,7 @@
       <c r="M71" s="6"/>
       <c r="N71" s="6"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="12"/>
       <c r="B72" s="12"/>
       <c r="C72" s="12"/>
@@ -5037,7 +5037,7 @@
       <c r="M72" s="6"/>
       <c r="N72" s="6"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="12"/>
       <c r="B73" s="12"/>
       <c r="C73" s="12"/>
@@ -5049,7 +5049,7 @@
       <c r="M73" s="6"/>
       <c r="N73" s="6"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="12"/>
       <c r="B74" s="12"/>
       <c r="C74" s="12"/>
@@ -5062,7 +5062,7 @@
       <c r="M74" s="6"/>
       <c r="N74" s="6"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="12"/>
       <c r="B75" s="12"/>
       <c r="C75" s="12"/>
@@ -5074,7 +5074,7 @@
       <c r="M75" s="6"/>
       <c r="N75" s="6"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="12"/>
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
@@ -5087,7 +5087,7 @@
       <c r="M76" s="6"/>
       <c r="N76" s="6"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="12"/>
       <c r="B77" s="12"/>
       <c r="C77" s="12"/>
@@ -5099,7 +5099,7 @@
       <c r="M77" s="6"/>
       <c r="N77" s="6"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="12"/>
       <c r="B78" s="12"/>
       <c r="C78" s="12"/>
@@ -5112,7 +5112,7 @@
       <c r="L78" s="6"/>
       <c r="M78" s="6"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="12"/>
       <c r="B79" s="12"/>
       <c r="C79" s="12"/>
@@ -5124,7 +5124,7 @@
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="12"/>
       <c r="B80" s="12"/>
       <c r="C80" s="12"/>
@@ -5137,7 +5137,7 @@
       <c r="L80" s="6"/>
       <c r="M80" s="6"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="12"/>
       <c r="B81" s="12"/>
       <c r="C81" s="12"/>
@@ -5149,7 +5149,7 @@
       <c r="L81" s="6"/>
       <c r="M81" s="6"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="12"/>
       <c r="B82" s="12"/>
       <c r="C82" s="12"/>
@@ -5162,7 +5162,7 @@
       <c r="L82" s="6"/>
       <c r="M82" s="6"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="12"/>
       <c r="B83" s="12"/>
       <c r="C83" s="12"/>
@@ -5174,7 +5174,7 @@
       <c r="L83" s="6"/>
       <c r="M83" s="6"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="12"/>
       <c r="B84" s="12"/>
       <c r="C84" s="12"/>
@@ -5187,7 +5187,7 @@
       <c r="L84" s="6"/>
       <c r="M84" s="6"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="12"/>
       <c r="B85" s="12"/>
       <c r="C85" s="12"/>
@@ -5199,7 +5199,7 @@
       <c r="L85" s="6"/>
       <c r="M85" s="6"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="12"/>
       <c r="B86" s="12"/>
       <c r="C86" s="12"/>
@@ -5212,7 +5212,7 @@
       <c r="L86" s="6"/>
       <c r="M86" s="6"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="12"/>
       <c r="B87" s="12"/>
       <c r="C87" s="12"/>
@@ -5224,7 +5224,7 @@
       <c r="L87" s="6"/>
       <c r="M87" s="6"/>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="12"/>
       <c r="B88" s="12"/>
       <c r="C88" s="12"/>
@@ -5237,7 +5237,7 @@
       <c r="L88" s="6"/>
       <c r="M88" s="6"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="12"/>
       <c r="B89" s="12"/>
       <c r="C89" s="12"/>
@@ -5249,7 +5249,7 @@
       <c r="L89" s="6"/>
       <c r="M89" s="6"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="12"/>
       <c r="B90" s="12"/>
       <c r="C90" s="12"/>
@@ -5262,7 +5262,7 @@
       <c r="L90" s="6"/>
       <c r="M90" s="6"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="12"/>
       <c r="B91" s="12"/>
       <c r="C91" s="12"/>
@@ -5274,7 +5274,7 @@
       <c r="L91" s="6"/>
       <c r="M91" s="6"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="12"/>
       <c r="B92" s="12"/>
       <c r="C92" s="12"/>
@@ -5287,7 +5287,7 @@
       <c r="L92" s="6"/>
       <c r="M92" s="6"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="12"/>
       <c r="B93" s="12"/>
       <c r="C93" s="12"/>
@@ -5299,7 +5299,7 @@
       <c r="L93" s="6"/>
       <c r="M93" s="6"/>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="12"/>
       <c r="B94" s="12"/>
       <c r="C94" s="12"/>
@@ -5312,7 +5312,7 @@
       <c r="L94" s="6"/>
       <c r="M94" s="6"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="12"/>
       <c r="B95" s="12"/>
       <c r="C95" s="12"/>
@@ -5324,7 +5324,7 @@
       <c r="L95" s="6"/>
       <c r="M95" s="6"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="12"/>
       <c r="B96" s="12"/>
       <c r="C96" s="12"/>
@@ -5337,7 +5337,7 @@
       <c r="L96" s="6"/>
       <c r="M96" s="6"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="12"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
@@ -5349,7 +5349,7 @@
       <c r="L97" s="6"/>
       <c r="M97" s="6"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="12"/>
       <c r="B98" s="12"/>
       <c r="C98" s="12"/>
@@ -5362,7 +5362,7 @@
       <c r="L98" s="6"/>
       <c r="M98" s="6"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="12"/>
       <c r="B99" s="12"/>
       <c r="C99" s="12"/>
@@ -5374,7 +5374,7 @@
       <c r="L99" s="6"/>
       <c r="M99" s="6"/>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="12"/>
       <c r="B100" s="12"/>
       <c r="C100" s="12"/>
@@ -5387,7 +5387,7 @@
       <c r="L100" s="6"/>
       <c r="M100" s="6"/>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="12"/>
       <c r="B101" s="12"/>
       <c r="C101" s="12"/>
@@ -5399,7 +5399,7 @@
       <c r="L101" s="6"/>
       <c r="M101" s="6"/>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="12"/>
       <c r="B102" s="12"/>
       <c r="C102" s="12"/>
@@ -5412,7 +5412,7 @@
       <c r="L102" s="6"/>
       <c r="M102" s="6"/>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="12"/>
       <c r="B103" s="12"/>
       <c r="C103" s="12"/>
@@ -5424,7 +5424,7 @@
       <c r="L103" s="6"/>
       <c r="M103" s="6"/>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="12"/>
       <c r="B104" s="12"/>
       <c r="C104" s="12"/>
@@ -5437,7 +5437,7 @@
       <c r="L104" s="6"/>
       <c r="M104" s="6"/>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="12"/>
       <c r="B105" s="12"/>
       <c r="C105" s="12"/>
@@ -5449,7 +5449,7 @@
       <c r="L105" s="6"/>
       <c r="M105" s="6"/>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="12"/>
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
@@ -5462,7 +5462,7 @@
       <c r="L106" s="6"/>
       <c r="M106" s="6"/>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="12"/>
       <c r="B107" s="12"/>
       <c r="C107" s="12"/>
@@ -5474,7 +5474,7 @@
       <c r="L107" s="6"/>
       <c r="M107" s="6"/>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="12"/>
       <c r="B108" s="12"/>
       <c r="C108" s="12"/>
@@ -5487,7 +5487,7 @@
       <c r="L108" s="6"/>
       <c r="M108" s="6"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="12"/>
       <c r="B109" s="12"/>
       <c r="C109" s="12"/>
@@ -5499,7 +5499,7 @@
       <c r="L109" s="6"/>
       <c r="M109" s="6"/>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="12"/>
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
@@ -5512,7 +5512,7 @@
       <c r="L110" s="6"/>
       <c r="M110" s="6"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="12"/>
       <c r="B111" s="12"/>
       <c r="C111" s="12"/>
@@ -5524,7 +5524,7 @@
       <c r="L111" s="6"/>
       <c r="M111" s="6"/>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="12"/>
       <c r="B112" s="12"/>
       <c r="C112" s="12"/>
@@ -5537,7 +5537,7 @@
       <c r="L112" s="6"/>
       <c r="M112" s="6"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="12"/>
       <c r="B113" s="12"/>
       <c r="C113" s="12"/>
@@ -5549,7 +5549,7 @@
       <c r="L113" s="6"/>
       <c r="M113" s="6"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="12"/>
       <c r="B114" s="12"/>
       <c r="C114" s="12"/>
@@ -5562,7 +5562,7 @@
       <c r="L114" s="6"/>
       <c r="M114" s="6"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="12"/>
       <c r="B115" s="12"/>
       <c r="C115" s="12"/>
@@ -5574,7 +5574,7 @@
       <c r="L115" s="6"/>
       <c r="M115" s="6"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="12"/>
       <c r="B116" s="12"/>
       <c r="C116" s="12"/>
@@ -5587,7 +5587,7 @@
       <c r="L116" s="6"/>
       <c r="M116" s="6"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="12"/>
       <c r="B117" s="12"/>
       <c r="C117" s="12"/>
@@ -5599,7 +5599,7 @@
       <c r="L117" s="6"/>
       <c r="M117" s="6"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="12"/>
       <c r="B118" s="12"/>
       <c r="C118" s="12"/>
@@ -5612,7 +5612,7 @@
       <c r="L118" s="6"/>
       <c r="M118" s="6"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="12"/>
       <c r="B119" s="12"/>
       <c r="C119" s="12"/>
@@ -5624,7 +5624,7 @@
       <c r="L119" s="6"/>
       <c r="M119" s="6"/>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="12"/>
       <c r="B120" s="12"/>
       <c r="C120" s="12"/>
@@ -5637,7 +5637,7 @@
       <c r="L120" s="6"/>
       <c r="M120" s="6"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="12"/>
       <c r="B121" s="12"/>
       <c r="C121" s="12"/>
@@ -5649,1281 +5649,1281 @@
       <c r="L121" s="6"/>
       <c r="M121" s="6"/>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="D122" s="6"/>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="D123" s="6"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="D124" s="6"/>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="D125" s="6"/>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="D126" s="6"/>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="D127" s="6"/>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="D128" s="6"/>
     </row>
-    <row r="129" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D129" s="6"/>
       <c r="H129" s="6"/>
     </row>
-    <row r="130" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D130" s="6"/>
     </row>
-    <row r="131" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D131" s="6"/>
     </row>
-    <row r="132" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D132" s="6"/>
     </row>
-    <row r="133" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D133" s="6"/>
     </row>
-    <row r="134" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D134" s="6"/>
     </row>
-    <row r="135" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D135" s="6"/>
     </row>
-    <row r="136" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D136" s="6"/>
     </row>
-    <row r="137" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D137" s="6"/>
     </row>
-    <row r="138" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D138" s="6"/>
     </row>
-    <row r="139" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D139" s="6"/>
     </row>
-    <row r="140" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D140" s="6"/>
     </row>
-    <row r="141" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D141" s="6"/>
     </row>
-    <row r="142" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D142" s="6"/>
     </row>
-    <row r="143" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D143" s="6"/>
     </row>
-    <row r="144" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D144" s="6"/>
     </row>
-    <row r="145" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D145" s="6"/>
     </row>
-    <row r="146" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D146" s="6"/>
     </row>
-    <row r="147" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D147" s="6"/>
     </row>
-    <row r="148" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D148" s="6"/>
     </row>
-    <row r="149" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D149" s="6"/>
     </row>
-    <row r="150" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D150" s="6"/>
     </row>
-    <row r="151" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D151" s="6"/>
     </row>
-    <row r="152" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D152" s="6"/>
     </row>
-    <row r="153" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D153" s="6"/>
     </row>
-    <row r="154" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D154" s="6"/>
     </row>
-    <row r="155" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D155" s="6"/>
     </row>
-    <row r="156" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D156" s="6"/>
     </row>
-    <row r="157" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D157" s="6"/>
     </row>
-    <row r="158" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D158" s="6"/>
     </row>
-    <row r="159" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D159" s="6"/>
     </row>
-    <row r="160" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D160" s="6"/>
     </row>
-    <row r="161" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D161" s="6"/>
       <c r="H161" s="6"/>
     </row>
-    <row r="162" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D162" s="6"/>
     </row>
-    <row r="163" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D163" s="6"/>
     </row>
-    <row r="164" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D164" s="6"/>
     </row>
-    <row r="165" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D165" s="6"/>
     </row>
-    <row r="166" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D166" s="6"/>
     </row>
-    <row r="167" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D167" s="6"/>
     </row>
-    <row r="168" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D168" s="6"/>
     </row>
-    <row r="169" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D169" s="6"/>
     </row>
-    <row r="170" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D170" s="6"/>
     </row>
-    <row r="171" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D171" s="6"/>
     </row>
-    <row r="172" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D172" s="6"/>
     </row>
-    <row r="173" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D173" s="6"/>
     </row>
-    <row r="174" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D174" s="6"/>
     </row>
-    <row r="175" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D175" s="6"/>
     </row>
-    <row r="176" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D176" s="6"/>
     </row>
-    <row r="177" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D177" s="6"/>
     </row>
-    <row r="178" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D178" s="6"/>
     </row>
-    <row r="179" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D179" s="6"/>
     </row>
-    <row r="180" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D180" s="6"/>
     </row>
-    <row r="181" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D181" s="6"/>
     </row>
-    <row r="182" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D182" s="6"/>
     </row>
-    <row r="183" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D183" s="6"/>
     </row>
-    <row r="184" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D184" s="6"/>
     </row>
-    <row r="185" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D185" s="6"/>
     </row>
-    <row r="186" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D186" s="6"/>
     </row>
-    <row r="187" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D187" s="6"/>
     </row>
-    <row r="188" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D188" s="6"/>
     </row>
-    <row r="189" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D189" s="6"/>
     </row>
-    <row r="190" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D190" s="6"/>
     </row>
-    <row r="191" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D191" s="6"/>
     </row>
-    <row r="192" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D192" s="6"/>
     </row>
-    <row r="193" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D193" s="6"/>
       <c r="H193" s="6"/>
     </row>
-    <row r="194" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D194" s="6"/>
     </row>
-    <row r="195" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D195" s="6"/>
     </row>
-    <row r="196" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D196" s="6"/>
     </row>
-    <row r="197" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D197" s="6"/>
     </row>
-    <row r="198" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D198" s="6"/>
     </row>
-    <row r="199" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D199" s="6"/>
     </row>
-    <row r="200" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D200" s="6"/>
     </row>
-    <row r="201" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D201" s="6"/>
     </row>
-    <row r="202" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D202" s="6"/>
     </row>
-    <row r="203" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D203" s="6"/>
     </row>
-    <row r="204" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D204" s="6"/>
     </row>
-    <row r="205" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D205" s="6"/>
     </row>
-    <row r="206" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D206" s="6"/>
     </row>
-    <row r="207" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D207" s="6"/>
     </row>
-    <row r="208" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D208" s="6"/>
     </row>
-    <row r="209" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D209" s="6"/>
     </row>
-    <row r="210" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="210" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D210" s="6"/>
     </row>
-    <row r="211" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D211" s="6"/>
     </row>
-    <row r="212" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D212" s="6"/>
     </row>
-    <row r="213" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D213" s="6"/>
     </row>
-    <row r="214" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D214" s="6"/>
     </row>
-    <row r="215" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D215" s="6"/>
     </row>
-    <row r="216" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D216" s="6"/>
     </row>
-    <row r="217" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D217" s="6"/>
     </row>
-    <row r="218" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D218" s="6"/>
     </row>
-    <row r="219" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D219" s="6"/>
     </row>
-    <row r="220" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D220" s="6"/>
     </row>
-    <row r="221" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D221" s="6"/>
     </row>
-    <row r="222" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D222" s="6"/>
     </row>
-    <row r="223" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D223" s="6"/>
     </row>
-    <row r="224" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D224" s="6"/>
     </row>
-    <row r="225" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="225" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D225" s="6"/>
       <c r="H225" s="6"/>
     </row>
-    <row r="226" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="226" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D226" s="6"/>
     </row>
-    <row r="227" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D227" s="6"/>
     </row>
-    <row r="228" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D228" s="6"/>
     </row>
-    <row r="229" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D229" s="6"/>
     </row>
-    <row r="230" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="230" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D230" s="6"/>
     </row>
-    <row r="231" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D231" s="6"/>
     </row>
-    <row r="232" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D232" s="6"/>
     </row>
-    <row r="233" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D233" s="6"/>
     </row>
-    <row r="234" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D234" s="6"/>
     </row>
-    <row r="235" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D235" s="6"/>
     </row>
-    <row r="236" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D236" s="6"/>
     </row>
-    <row r="237" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D237" s="6"/>
     </row>
-    <row r="238" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D238" s="6"/>
     </row>
-    <row r="239" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D239" s="6"/>
     </row>
-    <row r="240" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D240" s="6"/>
     </row>
-    <row r="241" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D241" s="6"/>
     </row>
-    <row r="242" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D242" s="6"/>
     </row>
-    <row r="243" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D243" s="6"/>
     </row>
-    <row r="244" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D244" s="6"/>
     </row>
-    <row r="245" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D245" s="6"/>
     </row>
-    <row r="246" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D246" s="6"/>
     </row>
-    <row r="247" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D247" s="6"/>
     </row>
-    <row r="248" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D248" s="6"/>
     </row>
-    <row r="249" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D249" s="6"/>
     </row>
-    <row r="250" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D250" s="6"/>
     </row>
-    <row r="251" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="251" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D251" s="6"/>
     </row>
-    <row r="252" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="252" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D252" s="6"/>
     </row>
-    <row r="253" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D253" s="6"/>
     </row>
-    <row r="254" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D254" s="6"/>
     </row>
-    <row r="255" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D255" s="6"/>
     </row>
-    <row r="256" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D256" s="6"/>
     </row>
-    <row r="257" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D257" s="6"/>
       <c r="H257" s="6"/>
     </row>
-    <row r="258" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D258" s="6"/>
     </row>
-    <row r="259" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D259" s="6"/>
     </row>
-    <row r="260" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="260" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D260" s="6"/>
     </row>
-    <row r="261" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="261" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D261" s="6"/>
     </row>
-    <row r="262" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="262" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D262" s="6"/>
     </row>
-    <row r="263" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D263" s="6"/>
     </row>
-    <row r="264" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D264" s="6"/>
     </row>
-    <row r="265" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D265" s="6"/>
     </row>
-    <row r="266" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D266" s="6"/>
     </row>
-    <row r="267" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D267" s="6"/>
     </row>
-    <row r="268" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D268" s="6"/>
     </row>
-    <row r="269" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D269" s="6"/>
     </row>
-    <row r="270" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D270" s="6"/>
     </row>
-    <row r="271" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="271" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D271" s="6"/>
     </row>
-    <row r="272" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="272" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D272" s="6"/>
     </row>
-    <row r="273" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D273" s="6"/>
     </row>
-    <row r="274" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D274" s="6"/>
     </row>
-    <row r="275" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D275" s="6"/>
     </row>
-    <row r="276" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D276" s="6"/>
     </row>
-    <row r="277" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D277" s="6"/>
     </row>
-    <row r="278" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D278" s="6"/>
     </row>
-    <row r="279" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D279" s="6"/>
     </row>
-    <row r="280" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="280" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D280" s="6"/>
     </row>
-    <row r="281" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="281" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D281" s="6"/>
     </row>
-    <row r="282" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D282" s="6"/>
     </row>
-    <row r="283" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D283" s="6"/>
     </row>
-    <row r="284" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D284" s="6"/>
     </row>
-    <row r="285" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D285" s="6"/>
     </row>
-    <row r="286" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D286" s="6"/>
     </row>
-    <row r="287" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D287" s="6"/>
     </row>
-    <row r="288" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D288" s="6"/>
     </row>
-    <row r="289" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="289" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D289" s="6"/>
       <c r="H289" s="6"/>
     </row>
-    <row r="290" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="290" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D290" s="6"/>
       <c r="H290" s="6"/>
     </row>
-    <row r="291" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D291" s="6"/>
       <c r="H291" s="6"/>
     </row>
-    <row r="292" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D292" s="6"/>
       <c r="H292" s="6"/>
     </row>
-    <row r="293" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D293" s="6"/>
       <c r="H293" s="6"/>
     </row>
-    <row r="294" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D294" s="6"/>
       <c r="H294" s="6"/>
     </row>
-    <row r="295" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D295" s="6"/>
       <c r="H295" s="6"/>
     </row>
-    <row r="296" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D296" s="6"/>
       <c r="H296" s="6"/>
     </row>
-    <row r="297" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D297" s="6"/>
       <c r="H297" s="6"/>
     </row>
-    <row r="298" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="298" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D298" s="6"/>
       <c r="H298" s="6"/>
     </row>
-    <row r="299" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="299" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D299" s="6"/>
       <c r="H299" s="6"/>
     </row>
-    <row r="300" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="300" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D300" s="6"/>
       <c r="H300" s="6"/>
     </row>
-    <row r="301" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="301" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D301" s="6"/>
       <c r="H301" s="6"/>
     </row>
-    <row r="302" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="302" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D302" s="6"/>
       <c r="H302" s="6"/>
     </row>
-    <row r="303" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="303" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D303" s="6"/>
       <c r="H303" s="6"/>
     </row>
-    <row r="304" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="304" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D304" s="6"/>
       <c r="H304" s="6"/>
     </row>
-    <row r="305" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="305" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D305" s="6"/>
       <c r="H305" s="6"/>
     </row>
-    <row r="306" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="306" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D306" s="6"/>
       <c r="H306" s="6"/>
     </row>
-    <row r="307" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="307" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D307" s="6"/>
       <c r="H307" s="6"/>
     </row>
-    <row r="308" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="308" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D308" s="6"/>
       <c r="H308" s="6"/>
     </row>
-    <row r="309" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="309" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D309" s="6"/>
       <c r="H309" s="6"/>
     </row>
-    <row r="310" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="310" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D310" s="6"/>
       <c r="H310" s="6"/>
     </row>
-    <row r="311" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="311" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D311" s="6"/>
       <c r="H311" s="6"/>
     </row>
-    <row r="312" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="312" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D312" s="6"/>
       <c r="H312" s="6"/>
     </row>
-    <row r="313" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="313" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D313" s="6"/>
       <c r="H313" s="6"/>
     </row>
-    <row r="314" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="314" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D314" s="6"/>
       <c r="H314" s="6"/>
     </row>
-    <row r="315" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="315" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D315" s="6"/>
       <c r="H315" s="6"/>
     </row>
-    <row r="316" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="316" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D316" s="6"/>
       <c r="H316" s="6"/>
     </row>
-    <row r="317" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="317" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D317" s="6"/>
       <c r="H317" s="6"/>
     </row>
-    <row r="318" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="318" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D318" s="6"/>
       <c r="H318" s="6"/>
     </row>
-    <row r="319" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="319" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D319" s="6"/>
       <c r="H319" s="6"/>
     </row>
-    <row r="320" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="320" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D320" s="6"/>
       <c r="H320" s="6"/>
     </row>
-    <row r="321" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="321" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D321" s="6"/>
       <c r="H321" s="6"/>
     </row>
-    <row r="322" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="322" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D322" s="6"/>
       <c r="H322" s="6"/>
     </row>
-    <row r="323" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="323" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D323" s="6"/>
       <c r="H323" s="6"/>
     </row>
-    <row r="324" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="324" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D324" s="6"/>
       <c r="H324" s="6"/>
     </row>
-    <row r="325" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="325" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D325" s="6"/>
       <c r="H325" s="6"/>
     </row>
-    <row r="326" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="326" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D326" s="6"/>
       <c r="H326" s="6"/>
     </row>
-    <row r="327" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="327" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D327" s="6"/>
       <c r="H327" s="6"/>
     </row>
-    <row r="328" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="328" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D328" s="6"/>
       <c r="H328" s="6"/>
     </row>
-    <row r="329" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="329" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D329" s="6"/>
       <c r="H329" s="6"/>
     </row>
-    <row r="330" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="330" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D330" s="6"/>
       <c r="H330" s="6"/>
     </row>
-    <row r="331" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="331" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D331" s="6"/>
       <c r="H331" s="6"/>
     </row>
-    <row r="332" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="332" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D332" s="6"/>
       <c r="H332" s="6"/>
     </row>
-    <row r="333" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="333" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D333" s="6"/>
       <c r="H333" s="6"/>
     </row>
-    <row r="334" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="334" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D334" s="6"/>
       <c r="H334" s="6"/>
     </row>
-    <row r="335" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="335" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D335" s="6"/>
       <c r="H335" s="6"/>
     </row>
-    <row r="336" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="336" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D336" s="6"/>
       <c r="H336" s="6"/>
     </row>
-    <row r="337" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="337" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D337" s="6"/>
       <c r="H337" s="6"/>
     </row>
-    <row r="338" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="338" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D338" s="6"/>
       <c r="H338" s="6"/>
     </row>
-    <row r="339" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="339" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D339" s="6"/>
       <c r="H339" s="6"/>
     </row>
-    <row r="340" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="340" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D340" s="6"/>
       <c r="H340" s="6"/>
     </row>
-    <row r="341" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="341" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D341" s="6"/>
       <c r="H341" s="6"/>
     </row>
-    <row r="342" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D342" s="6"/>
       <c r="H342" s="6"/>
     </row>
-    <row r="343" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="343" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D343" s="6"/>
       <c r="H343" s="6"/>
     </row>
-    <row r="344" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="344" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D344" s="6"/>
       <c r="H344" s="6"/>
     </row>
-    <row r="345" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="345" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D345" s="6"/>
       <c r="H345" s="6"/>
     </row>
-    <row r="346" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="346" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D346" s="6"/>
       <c r="H346" s="6"/>
     </row>
-    <row r="347" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="347" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D347" s="6"/>
       <c r="H347" s="6"/>
     </row>
-    <row r="348" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="348" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D348" s="6"/>
       <c r="H348" s="6"/>
     </row>
-    <row r="349" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="349" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D349" s="6"/>
       <c r="H349" s="6"/>
     </row>
-    <row r="350" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="350" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D350" s="6"/>
       <c r="H350" s="6"/>
     </row>
-    <row r="351" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="351" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D351" s="6"/>
       <c r="H351" s="6"/>
     </row>
-    <row r="352" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="352" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D352" s="6"/>
       <c r="H352" s="6"/>
     </row>
-    <row r="353" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="353" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D353" s="6"/>
       <c r="H353" s="6"/>
     </row>
-    <row r="354" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="354" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D354" s="6"/>
       <c r="H354" s="6"/>
     </row>
-    <row r="355" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="355" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D355" s="6"/>
       <c r="H355" s="6"/>
     </row>
-    <row r="356" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="356" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D356" s="6"/>
       <c r="H356" s="6"/>
     </row>
-    <row r="357" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="357" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D357" s="6"/>
       <c r="H357" s="6"/>
     </row>
-    <row r="358" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="358" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D358" s="6"/>
       <c r="H358" s="6"/>
     </row>
-    <row r="359" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="359" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D359" s="6"/>
       <c r="H359" s="6"/>
     </row>
-    <row r="360" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="360" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D360" s="6"/>
       <c r="H360" s="6"/>
     </row>
-    <row r="361" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="361" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D361" s="6"/>
       <c r="H361" s="6"/>
     </row>
-    <row r="362" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="362" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D362" s="6"/>
       <c r="H362" s="6"/>
     </row>
-    <row r="363" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="363" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D363" s="6"/>
       <c r="H363" s="6"/>
     </row>
-    <row r="364" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="364" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D364" s="6"/>
       <c r="H364" s="6"/>
     </row>
-    <row r="365" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="365" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D365" s="6"/>
       <c r="H365" s="6"/>
     </row>
-    <row r="366" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="366" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D366" s="6"/>
       <c r="H366" s="6"/>
     </row>
-    <row r="367" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="367" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D367" s="6"/>
       <c r="H367" s="6"/>
     </row>
-    <row r="368" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="368" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D368" s="6"/>
       <c r="H368" s="6"/>
     </row>
-    <row r="369" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="369" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D369" s="6"/>
       <c r="H369" s="6"/>
     </row>
-    <row r="370" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="370" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D370" s="6"/>
       <c r="H370" s="6"/>
     </row>
-    <row r="371" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="371" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D371" s="6"/>
       <c r="H371" s="6"/>
     </row>
-    <row r="372" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="372" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D372" s="6"/>
       <c r="H372" s="6"/>
     </row>
-    <row r="373" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="373" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D373" s="6"/>
       <c r="H373" s="6"/>
     </row>
-    <row r="374" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="374" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D374" s="6"/>
       <c r="H374" s="6"/>
     </row>
-    <row r="375" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="375" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D375" s="6"/>
       <c r="H375" s="6"/>
     </row>
-    <row r="376" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="376" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D376" s="6"/>
       <c r="H376" s="6"/>
     </row>
-    <row r="377" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="377" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D377" s="6"/>
       <c r="H377" s="6"/>
     </row>
-    <row r="378" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="378" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D378" s="6"/>
       <c r="H378" s="6"/>
     </row>
-    <row r="379" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="379" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D379" s="6"/>
       <c r="H379" s="6"/>
     </row>
-    <row r="380" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="380" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D380" s="6"/>
       <c r="H380" s="6"/>
     </row>
-    <row r="381" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="381" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D381" s="6"/>
       <c r="H381" s="6"/>
     </row>
-    <row r="382" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="382" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D382" s="6"/>
       <c r="H382" s="6"/>
     </row>
-    <row r="383" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="383" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D383" s="6"/>
       <c r="H383" s="6"/>
     </row>
-    <row r="384" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="384" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D384" s="6"/>
       <c r="H384" s="6"/>
     </row>
-    <row r="385" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="385" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D385" s="6"/>
       <c r="H385" s="6"/>
     </row>
-    <row r="386" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="386" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D386" s="6"/>
       <c r="H386" s="6"/>
     </row>
-    <row r="387" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="387" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D387" s="6"/>
       <c r="H387" s="6"/>
     </row>
-    <row r="388" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="388" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D388" s="6"/>
       <c r="H388" s="6"/>
     </row>
-    <row r="389" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="389" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D389" s="6"/>
       <c r="H389" s="6"/>
     </row>
-    <row r="390" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="390" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D390" s="6"/>
       <c r="H390" s="6"/>
     </row>
-    <row r="391" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="391" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D391" s="6"/>
       <c r="H391" s="6"/>
     </row>
-    <row r="392" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="392" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D392" s="6"/>
       <c r="H392" s="6"/>
     </row>
-    <row r="393" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="393" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D393" s="6"/>
       <c r="H393" s="6"/>
     </row>
-    <row r="394" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="394" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D394" s="6"/>
       <c r="H394" s="6"/>
     </row>
-    <row r="395" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="395" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D395" s="6"/>
       <c r="H395" s="6"/>
     </row>
-    <row r="396" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="396" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D396" s="6"/>
       <c r="H396" s="6"/>
     </row>
-    <row r="397" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="397" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D397" s="6"/>
       <c r="H397" s="6"/>
     </row>
-    <row r="398" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="398" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D398" s="6"/>
       <c r="H398" s="6"/>
     </row>
-    <row r="399" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="399" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D399" s="6"/>
       <c r="H399" s="6"/>
     </row>
-    <row r="400" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="400" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D400" s="6"/>
       <c r="H400" s="6"/>
     </row>
-    <row r="401" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="401" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D401" s="6"/>
       <c r="H401" s="6"/>
     </row>
-    <row r="402" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="402" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D402" s="6"/>
       <c r="H402" s="6"/>
     </row>
-    <row r="403" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="403" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D403" s="6"/>
       <c r="H403" s="6"/>
     </row>
-    <row r="404" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="404" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D404" s="6"/>
       <c r="H404" s="6"/>
     </row>
-    <row r="405" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="405" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D405" s="6"/>
       <c r="H405" s="6"/>
     </row>
-    <row r="406" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="406" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D406" s="6"/>
       <c r="H406" s="6"/>
     </row>
-    <row r="407" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="407" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D407" s="6"/>
       <c r="H407" s="6"/>
     </row>
-    <row r="408" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="408" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D408" s="6"/>
       <c r="H408" s="6"/>
     </row>
-    <row r="409" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="409" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D409" s="6"/>
       <c r="H409" s="6"/>
     </row>
-    <row r="410" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="410" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D410" s="6"/>
       <c r="H410" s="6"/>
     </row>
-    <row r="411" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="411" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D411" s="6"/>
       <c r="H411" s="6"/>
     </row>
-    <row r="412" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="412" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D412" s="6"/>
       <c r="H412" s="6"/>
     </row>
-    <row r="413" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="413" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D413" s="6"/>
       <c r="H413" s="6"/>
     </row>
-    <row r="414" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="414" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D414" s="6"/>
       <c r="H414" s="6"/>
     </row>
-    <row r="415" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="415" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D415" s="6"/>
       <c r="H415" s="6"/>
     </row>
-    <row r="416" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="416" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D416" s="6"/>
       <c r="H416" s="6"/>
     </row>
-    <row r="417" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="417" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D417" s="6"/>
       <c r="H417" s="6"/>
     </row>
-    <row r="418" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="418" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D418" s="6"/>
       <c r="H418" s="6"/>
     </row>
-    <row r="419" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="419" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D419" s="6"/>
       <c r="H419" s="6"/>
     </row>
-    <row r="420" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="420" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D420" s="6"/>
       <c r="H420" s="6"/>
     </row>
-    <row r="421" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="421" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D421" s="6"/>
       <c r="H421" s="6"/>
     </row>
-    <row r="422" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="422" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D422" s="6"/>
       <c r="H422" s="6"/>
     </row>
-    <row r="423" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="423" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D423" s="6"/>
       <c r="H423" s="6"/>
     </row>
-    <row r="424" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="424" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D424" s="6"/>
       <c r="H424" s="6"/>
     </row>
-    <row r="425" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="425" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D425" s="6"/>
       <c r="H425" s="6"/>
     </row>
-    <row r="426" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="426" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D426" s="6"/>
       <c r="H426" s="6"/>
     </row>
-    <row r="427" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="427" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D427" s="6"/>
       <c r="H427" s="6"/>
     </row>
-    <row r="428" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="428" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D428" s="6"/>
       <c r="H428" s="6"/>
     </row>
-    <row r="429" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="429" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D429" s="6"/>
       <c r="H429" s="6"/>
     </row>
-    <row r="430" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="430" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D430" s="6"/>
       <c r="H430" s="6"/>
     </row>
-    <row r="431" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="431" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D431" s="6"/>
       <c r="H431" s="6"/>
     </row>
-    <row r="432" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="432" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D432" s="6"/>
       <c r="H432" s="6"/>
     </row>
-    <row r="433" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="433" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D433" s="6"/>
       <c r="H433" s="6"/>
     </row>
-    <row r="434" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="434" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D434" s="6"/>
       <c r="H434" s="6"/>
     </row>
-    <row r="435" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="435" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D435" s="6"/>
       <c r="H435" s="6"/>
     </row>
-    <row r="436" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="436" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D436" s="6"/>
       <c r="H436" s="6"/>
     </row>
-    <row r="437" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="437" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D437" s="6"/>
       <c r="H437" s="6"/>
     </row>
-    <row r="438" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="438" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D438" s="6"/>
       <c r="H438" s="6"/>
     </row>
-    <row r="439" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="439" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D439" s="6"/>
       <c r="H439" s="6"/>
     </row>
-    <row r="440" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="440" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D440" s="6"/>
       <c r="H440" s="6"/>
     </row>
-    <row r="441" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="441" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D441" s="6"/>
       <c r="H441" s="6"/>
     </row>
-    <row r="442" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="442" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D442" s="6"/>
       <c r="H442" s="6"/>
     </row>
-    <row r="443" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="443" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D443" s="6"/>
       <c r="H443" s="6"/>
     </row>
-    <row r="444" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="444" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D444" s="6"/>
       <c r="H444" s="6"/>
     </row>
-    <row r="445" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="445" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D445" s="6"/>
       <c r="H445" s="6"/>
     </row>
-    <row r="446" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="446" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D446" s="6"/>
       <c r="H446" s="6"/>
     </row>
-    <row r="447" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="447" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D447" s="6"/>
       <c r="H447" s="6"/>
     </row>
-    <row r="448" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="448" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D448" s="6"/>
       <c r="H448" s="6"/>
     </row>
-    <row r="449" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="449" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D449" s="6"/>
       <c r="H449" s="6"/>
     </row>
-    <row r="450" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="450" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D450" s="6"/>
       <c r="H450" s="6"/>
     </row>
-    <row r="451" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="451" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D451" s="6"/>
       <c r="H451" s="6"/>
     </row>
-    <row r="452" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="452" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D452" s="6"/>
       <c r="H452" s="6"/>
     </row>
-    <row r="453" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="453" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D453" s="6"/>
       <c r="H453" s="6"/>
     </row>
-    <row r="454" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="454" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D454" s="6"/>
       <c r="H454" s="6"/>
     </row>
-    <row r="455" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="455" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D455" s="6"/>
       <c r="H455" s="6"/>
     </row>
-    <row r="456" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="456" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D456" s="6"/>
       <c r="H456" s="6"/>
     </row>
-    <row r="457" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="457" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D457" s="6"/>
       <c r="H457" s="6"/>
     </row>
-    <row r="458" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="458" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D458" s="6"/>
       <c r="H458" s="6"/>
     </row>
-    <row r="459" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="459" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D459" s="6"/>
       <c r="H459" s="6"/>
     </row>
-    <row r="460" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="460" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D460" s="6"/>
       <c r="H460" s="6"/>
     </row>
-    <row r="461" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="461" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D461" s="6"/>
       <c r="H461" s="6"/>
     </row>
-    <row r="462" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="462" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D462" s="6"/>
       <c r="H462" s="6"/>
     </row>
-    <row r="463" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="463" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D463" s="6"/>
       <c r="H463" s="6"/>
     </row>
-    <row r="464" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="464" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D464" s="6"/>
       <c r="H464" s="6"/>
     </row>
-    <row r="465" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="465" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D465" s="6"/>
       <c r="H465" s="6"/>
     </row>
-    <row r="466" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="466" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D466" s="6"/>
       <c r="H466" s="6"/>
     </row>
-    <row r="467" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="467" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D467" s="6"/>
       <c r="H467" s="6"/>
     </row>
-    <row r="468" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="468" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D468" s="6"/>
       <c r="H468" s="6"/>
     </row>
-    <row r="469" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="469" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D469" s="6"/>
       <c r="H469" s="6"/>
     </row>
-    <row r="470" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="470" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D470" s="6"/>
       <c r="H470" s="6"/>
     </row>
-    <row r="471" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="471" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D471" s="6"/>
       <c r="H471" s="6"/>
     </row>
-    <row r="472" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="472" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D472" s="6"/>
       <c r="H472" s="6"/>
     </row>
-    <row r="473" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="473" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D473" s="6"/>
       <c r="H473" s="6"/>
     </row>
-    <row r="474" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="474" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D474" s="6"/>
       <c r="H474" s="6"/>
     </row>
-    <row r="475" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="475" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D475" s="6"/>
       <c r="H475" s="6"/>
     </row>
-    <row r="476" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="476" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D476" s="6"/>
       <c r="H476" s="6"/>
     </row>
-    <row r="477" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="477" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D477" s="6"/>
       <c r="H477" s="6"/>
     </row>
-    <row r="478" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="478" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D478" s="6"/>
       <c r="H478" s="6"/>
     </row>
-    <row r="479" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="479" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D479" s="6"/>
       <c r="H479" s="6"/>
     </row>
-    <row r="480" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="480" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D480" s="6"/>
       <c r="H480" s="6"/>
     </row>
-    <row r="481" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="481" spans="4:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D481" s="6"/>
       <c r="H481" s="6"/>
     </row>
@@ -6936,9 +6936,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B5:M8"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="2" t="s">
         <v>21</v>
       </c>
@@ -6976,7 +6976,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="13">
         <v>43672</v>
       </c>
@@ -6999,7 +6999,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="13">
         <v>43684</v>
       </c>
@@ -7030,9 +7030,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:P3"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="2" t="s">
         <v>34</v>
       </c>
@@ -7079,7 +7079,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" t="s">
         <v>19</v>
       </c>
